--- a/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
+++ b/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>D(4turn)</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -46,6 +46,9 @@
   <si>
     <t>Sim(4turn)</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beta</t>
   </si>
 </sst>
 </file>
@@ -747,7 +750,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.0912232630818717E-2"/>
+          <c:y val="0.13769273288996337"/>
+          <c:w val="0.91585780804243277"/>
+          <c:h val="0.7452794761754562"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1197,6 +1210,172 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$P$2:$P$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>135.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130.66999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>126.32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>122.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>117.85</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>113.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>109.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>106.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>102.72</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>99.49</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>96.52</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>93.85</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>91.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>89.47</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>87.79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>86.47</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>85.52</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>84.95</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>84.76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$Y$2:$Y$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>135.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>117.66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100.39</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83.39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66.790000000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.57</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-6.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-17.850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-28.45</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-37.81</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-45.85</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-52.51</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-57.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-61.52</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-63.79</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-64.55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -1206,11 +1385,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1811724800"/>
-        <c:axId val="1811723168"/>
+        <c:axId val="-74225200"/>
+        <c:axId val="-74234448"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1811724800"/>
+        <c:axId val="-74225200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1253,7 +1432,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811723168"/>
+        <c:crossAx val="-74234448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1261,7 +1440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1811723168"/>
+        <c:axId val="-74234448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1312,7 +1491,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811724800"/>
+        <c:crossAx val="-74225200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1407,37 +1586,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -1448,7 +1596,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>sim</c:v>
+            <c:strRef>
+              <c:f>Lambda_d_matrix!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>D(4turn)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1464,148 +1620,103 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:f>Lambda_d_matrix!$O$1:$Y$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>90</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>95</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>105</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>110</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>115</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>120</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>125</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>130</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>135</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>140</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>145</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>155</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>170</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>180</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$C$2:$C$20</c:f>
+              <c:f>Lambda_d_matrix!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>44.6</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.44</c:v>
+                  <c:v>134.99</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.94</c:v>
+                  <c:v>134.94</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.1</c:v>
+                  <c:v>134.08000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41.93</c:v>
+                  <c:v>131.88</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.44</c:v>
+                  <c:v>129.15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38.630000000000003</c:v>
+                  <c:v>126.69</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.53</c:v>
+                  <c:v>124.73</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>34.14</c:v>
+                  <c:v>122.91</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>31.5</c:v>
+                  <c:v>121.08</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>28.61</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>25.51</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>22.22</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>18.77</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15.18</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>11.48</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.69</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3.85</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-0.01</c:v>
+                  <c:v>119.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-72AB-4D33-ADCA-B063982056BD}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>blog</c:v>
+            <c:strRef>
+              <c:f>Lambda_d_matrix!$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>d(blog)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1619,84 +1730,105 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$C$23:$C$41</c:f>
+              <c:f>Lambda_d_matrix!$B$23:$L$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>53.96</c:v>
+                  <c:v>135.87</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54.15</c:v>
+                  <c:v>142.15</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.45</c:v>
+                  <c:v>141.69</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>53.61</c:v>
+                  <c:v>139.61000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>53.69</c:v>
+                  <c:v>137.36000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51.73</c:v>
+                  <c:v>135.22</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50.69</c:v>
+                  <c:v>132.78</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>48.05</c:v>
+                  <c:v>130.58000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46.29</c:v>
+                  <c:v>128.37</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>43.17</c:v>
+                  <c:v>125.11</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35.700000000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>32.47</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28.67</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>24.79</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.170000000000002</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15.42</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>10.6</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.2</c:v>
+                  <c:v>122.91</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-72AB-4D33-ADCA-B063982056BD}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>blog</c:v>
+            <c:strRef>
+              <c:f>Lambda_d_matrix!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1710,84 +1842,105 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$L$23:$L$41</c:f>
+              <c:f>Lambda_d_matrix!$O$2:$Y$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>263.44</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>261.91000000000003</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>260.39</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>258.88</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>255.29</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>250.66</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>246.07</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>239.41</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>232.33</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>220.15</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>209.66</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>196.58</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>180.04</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>159.79</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>135.16</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>106.69</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>74.83</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>41.68</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.51</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-72AB-4D33-ADCA-B063982056BD}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:v>sim</c:v>
+            <c:strRef>
+              <c:f>Lambda_d_matrix!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>D(4turn)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1801,78 +1954,315 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$L$2:$L$20</c:f>
+              <c:f>Lambda_d_matrix!$B$20:$L$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>246.89</c:v>
+                  <c:v>135.05000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>248.04</c:v>
+                  <c:v>117.55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>248.29</c:v>
+                  <c:v>100.14</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>247.56</c:v>
+                  <c:v>82.95</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>245.81</c:v>
+                  <c:v>66.430000000000007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>242.94</c:v>
+                  <c:v>50.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>238.77</c:v>
+                  <c:v>34.33</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>233.16</c:v>
+                  <c:v>18.559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>226.02</c:v>
+                  <c:v>2.98</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>217.23</c:v>
+                  <c:v>-12.44</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>206.4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>192.03</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>173.53</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>153.05000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>129.46</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>101.48</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>69.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>35.14</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-0.03</c:v>
+                  <c:v>-27.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-72AB-4D33-ADCA-B063982056BD}"/>
-            </c:ext>
-          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Lambda_d_matrix!$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>d(blog)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$B$41:$L$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>135.87</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>118.47</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100.57</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66.540000000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>49.89</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.93</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-10.31</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-23.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Lambda_d_matrix!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$O$20:$Y$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>135.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>84.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.89</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.65</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-6.92</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-22.65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-37.31</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-51.19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-64.55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1883,11 +2273,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1811732960"/>
-        <c:axId val="1811735680"/>
+        <c:axId val="-148748112"/>
+        <c:axId val="-148751920"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1811732960"/>
+        <c:axId val="-148748112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1930,7 +2320,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811735680"/>
+        <c:crossAx val="-148751920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1938,7 +2328,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1811735680"/>
+        <c:axId val="-148751920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1989,7 +2379,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811732960"/>
+        <c:crossAx val="-148748112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2136,44 +2526,86 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$B$20:$L$20</c:f>
+              <c:f>'Lamgda_q(mWb)'!$O$1:$Y$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>117.55</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100.14</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82.95</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66.430000000000007</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.27</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34.33</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.559999999999999</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.98</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-12.44</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-27.64</c:v>
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$B$23:$L$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>104.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>141.29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>166.96</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>185.54</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>205.43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>223.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>241.48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>253.39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>263.44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2183,9 +2615,6 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:v>blog(90)</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2198,44 +2627,86 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$B$41:$L$41</c:f>
+              <c:f>'Lamgda_q(mWb)'!$O$1:$Y$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.87</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118.47</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100.57</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83.25</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66.540000000000006</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>49.89</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34.06</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.93</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.18</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-10.31</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-23.99</c:v>
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$B$2:$L$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>88.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>127.61</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>156.86000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179.23</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>197.21</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>211.84</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>224.67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>236.19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>246.89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2257,44 +2728,86 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$B$2:$L$2</c:f>
+              <c:f>'Lamgda_q(mWb)'!$O$1:$Y$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134.99</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>134.94</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>134.08000000000001</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.88</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>129.15</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>126.69</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>124.73</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>122.91</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>121.08</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>119.25</c:v>
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$B$19:$L$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.53</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.91</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22.44</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25.79</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29.01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32.119999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35.14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2304,9 +2817,6 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
-          <c:tx>
-            <c:v>blog</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2319,44 +2829,299 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$B$23:$L$23</c:f>
+              <c:f>'Lamgda_q(mWb)'!$O$1:$Y$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.87</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>142.15</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>141.69</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139.61000000000001</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>137.36000000000001</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>135.22</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>132.78</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>130.58000000000001</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>128.37</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>125.11</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>122.91</c:v>
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$B$40:$L$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.95</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.81</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34.61</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>38.97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>41.68</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$O$2:$Y$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>116.55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>144.27000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>168.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>207.22</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>222.05</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>235.76</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>248.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$O$1:$Y$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$O$19:$Y$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.52</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.58</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.72</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.36</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.55</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2372,16 +3137,17 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1811727520"/>
-        <c:axId val="1811737312"/>
+        <c:axId val="-74236624"/>
+        <c:axId val="-74233360"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1811727520"/>
+        <c:axId val="-74236624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2418,7 +3184,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811737312"/>
+        <c:crossAx val="-74233360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2426,7 +3192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1811737312"/>
+        <c:axId val="-74233360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2477,7 +3243,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811727520"/>
+        <c:crossAx val="-74236624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2489,6 +3255,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2540,37 +3338,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -2580,6 +3347,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Q(turn)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2592,44 +3370,134 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$B$23:$L$23</c:f>
+              <c:f>'Lamgda_q(mWb)'!$L$2:$L$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>246.89</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.96</c:v>
+                  <c:v>248.04</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>104.1</c:v>
+                  <c:v>248.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>141.29</c:v>
+                  <c:v>247.56</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>166.96</c:v>
+                  <c:v>245.81</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>185.54</c:v>
+                  <c:v>242.94</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>205.43</c:v>
+                  <c:v>238.77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>223.55</c:v>
+                  <c:v>233.16</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>241.48</c:v>
+                  <c:v>226.02</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>253.39</c:v>
+                  <c:v>217.23</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>263.44</c:v>
+                  <c:v>206.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>192.03</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>173.53</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>153.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>129.46</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>101.48</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>69.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.14</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2639,6 +3507,17 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>q(blog)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2651,44 +3530,134 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$B$2:$L$2</c:f>
+              <c:f>'Lamgda_q(mWb)'!$L$23:$L$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>-0.01</c:v>
+                  <c:v>263.44</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.6</c:v>
+                  <c:v>261.91000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.64</c:v>
+                  <c:v>260.39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>127.61</c:v>
+                  <c:v>258.88</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>156.86000000000001</c:v>
+                  <c:v>255.29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>179.23</c:v>
+                  <c:v>250.66</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>197.21</c:v>
+                  <c:v>246.07</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>211.84</c:v>
+                  <c:v>239.41</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>224.67</c:v>
+                  <c:v>232.33</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>236.19</c:v>
+                  <c:v>220.15</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>246.89</c:v>
+                  <c:v>209.66</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>196.58</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>180.04</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>159.79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>135.16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>106.69</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74.83</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>41.68</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.51</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2698,6 +3667,17 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2710,44 +3690,134 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$B$19:$L$19</c:f>
+              <c:f>'Lamgda_q(mWb)'!$Y$2:$Y$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>-0.01</c:v>
+                  <c:v>248.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.85</c:v>
+                  <c:v>247.81</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.73</c:v>
+                  <c:v>244.97</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.53</c:v>
+                  <c:v>240.28</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.23</c:v>
+                  <c:v>233.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18.91</c:v>
+                  <c:v>225.45</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>22.44</c:v>
+                  <c:v>215.43</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.79</c:v>
+                  <c:v>203.77</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29.01</c:v>
+                  <c:v>190.56</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>32.119999999999997</c:v>
+                  <c:v>175.9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35.14</c:v>
+                  <c:v>159.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>142.68</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>124.38</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>105.13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>85.08</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>64.38</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>21.68</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2757,6 +3827,17 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Q(turn)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2769,44 +3850,454 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Lamgda_q(mWb)'!$B$40:$L$40</c:f>
+              <c:f>'Lamgda_q(mWb)'!$C$2:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.44</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43.94</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41.93</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38.630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.53</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34.14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>28.61</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25.51</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22.22</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18.77</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11.48</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.69</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>q(blog)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$C$23:$C$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>53.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53.61</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.69</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.69</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>48.05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46.29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>43.17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32.47</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>28.67</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>24.79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.170000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lamgda_q(mWb)'!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$A$23:$A$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lamgda_q(mWb)'!$P$2:$P$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>51.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50.81</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49.84</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48.48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.76</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44.68</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42.26</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39.520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>33.17</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29.59</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.81</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>13.35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.9600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15.95</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.22</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>24.15</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>27.81</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>31.8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>34.61</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>38.97</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>41.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2822,16 +4313,17 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1811736224"/>
-        <c:axId val="1811735136"/>
+        <c:axId val="-67944288"/>
+        <c:axId val="-67939936"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1811736224"/>
+        <c:axId val="-67944288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2868,7 +4360,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811735136"/>
+        <c:crossAx val="-67939936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2876,7 +4368,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1811735136"/>
+        <c:axId val="-67939936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2927,7 +4419,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811736224"/>
+        <c:crossAx val="-67944288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2939,6 +4431,38 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -3401,11 +4925,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1811736768"/>
-        <c:axId val="1811737856"/>
+        <c:axId val="-74234992"/>
+        <c:axId val="-74232816"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1811736768"/>
+        <c:axId val="-74234992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3447,7 +4971,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811737856"/>
+        <c:crossAx val="-74232816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3455,7 +4979,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1811737856"/>
+        <c:axId val="-74232816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3506,7 +5030,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811736768"/>
+        <c:crossAx val="-74234992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3864,11 +5388,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1811723712"/>
-        <c:axId val="1811733504"/>
+        <c:axId val="-74231728"/>
+        <c:axId val="-74231184"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1811723712"/>
+        <c:axId val="-74231728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3910,7 +5434,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811733504"/>
+        <c:crossAx val="-74231184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3918,7 +5442,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1811733504"/>
+        <c:axId val="-74231184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3969,7 +5493,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1811723712"/>
+        <c:crossAx val="-74231728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7358,16 +8882,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>603079</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>197734</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>276218</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>199450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>446195</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>444525</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>134980</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7388,20 +8912,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>439066</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>33719</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>288224</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95758</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>46861</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>184388</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>363683</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>87099</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="차트 2"/>
+        <xdr:cNvPr id="5" name="차트 4"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -7423,20 +8947,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>214746</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>98052</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>53789</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>196613</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>123418</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>639536</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="차트 1"/>
+        <xdr:cNvPr id="3" name="차트 2"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -7456,22 +8980,20 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>165847</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>151329</xdr:rowOff>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>261810</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>66368</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>598713</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="차트 2"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="차트 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7816,10 +9338,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7856,8 +9378,44 @@
       <c r="L1">
         <v>340</v>
       </c>
+      <c r="N1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <v>34</v>
+      </c>
+      <c r="Q1">
+        <v>68</v>
+      </c>
+      <c r="R1">
+        <v>102</v>
+      </c>
+      <c r="S1">
+        <v>136</v>
+      </c>
+      <c r="T1">
+        <v>170</v>
+      </c>
+      <c r="U1">
+        <v>204</v>
+      </c>
+      <c r="V1">
+        <v>238</v>
+      </c>
+      <c r="W1">
+        <v>272</v>
+      </c>
+      <c r="X1">
+        <v>306</v>
+      </c>
+      <c r="Y1">
+        <v>340</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
@@ -7894,8 +9452,44 @@
       <c r="L2">
         <v>119.25</v>
       </c>
+      <c r="N2">
+        <v>90</v>
+      </c>
+      <c r="O2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="R2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="S2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="T2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="U2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="V2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="W2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="X2">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="Y2">
+        <v>135.05000000000001</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
@@ -7932,8 +9526,44 @@
       <c r="L3">
         <v>109.32</v>
       </c>
+      <c r="N3">
+        <v>95</v>
+      </c>
+      <c r="O3">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P3">
+        <v>130.66999999999999</v>
+      </c>
+      <c r="Q3">
+        <v>128.65</v>
+      </c>
+      <c r="R3">
+        <v>126.93</v>
+      </c>
+      <c r="S3">
+        <v>125.47</v>
+      </c>
+      <c r="T3">
+        <v>124.12</v>
+      </c>
+      <c r="U3">
+        <v>122.67</v>
+      </c>
+      <c r="V3">
+        <v>121.3</v>
+      </c>
+      <c r="W3">
+        <v>120.03</v>
+      </c>
+      <c r="X3">
+        <v>118.82</v>
+      </c>
+      <c r="Y3">
+        <v>117.66</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -7970,8 +9600,44 @@
       <c r="L4">
         <v>98.88</v>
       </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P4">
+        <v>126.32</v>
+      </c>
+      <c r="Q4">
+        <v>122.31</v>
+      </c>
+      <c r="R4">
+        <v>118.87</v>
+      </c>
+      <c r="S4">
+        <v>115.97</v>
+      </c>
+      <c r="T4">
+        <v>113.27</v>
+      </c>
+      <c r="U4">
+        <v>110.39</v>
+      </c>
+      <c r="V4">
+        <v>107.67</v>
+      </c>
+      <c r="W4">
+        <v>105.12</v>
+      </c>
+      <c r="X4">
+        <v>102.71</v>
+      </c>
+      <c r="Y4">
+        <v>100.39</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
@@ -8008,8 +9674,44 @@
       <c r="L5">
         <v>88.03</v>
       </c>
+      <c r="N5">
+        <v>105</v>
+      </c>
+      <c r="O5">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P5">
+        <v>122.03</v>
+      </c>
+      <c r="Q5">
+        <v>116.06</v>
+      </c>
+      <c r="R5">
+        <v>110.94</v>
+      </c>
+      <c r="S5">
+        <v>106.61</v>
+      </c>
+      <c r="T5">
+        <v>102.59</v>
+      </c>
+      <c r="U5">
+        <v>98.3</v>
+      </c>
+      <c r="V5">
+        <v>94.23</v>
+      </c>
+      <c r="W5">
+        <v>90.44</v>
+      </c>
+      <c r="X5">
+        <v>86.85</v>
+      </c>
+      <c r="Y5">
+        <v>83.39</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
@@ -8046,8 +9748,44 @@
       <c r="L6">
         <v>77.23</v>
       </c>
+      <c r="N6">
+        <v>110</v>
+      </c>
+      <c r="O6">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P6">
+        <v>117.85</v>
+      </c>
+      <c r="Q6">
+        <v>109.95</v>
+      </c>
+      <c r="R6">
+        <v>103.19</v>
+      </c>
+      <c r="S6">
+        <v>97.47</v>
+      </c>
+      <c r="T6">
+        <v>92.16</v>
+      </c>
+      <c r="U6">
+        <v>86.49</v>
+      </c>
+      <c r="V6">
+        <v>81.11</v>
+      </c>
+      <c r="W6">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="X6">
+        <v>71.349999999999994</v>
+      </c>
+      <c r="Y6">
+        <v>66.790000000000006</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
@@ -8084,8 +9822,44 @@
       <c r="L7">
         <v>66.69</v>
       </c>
+      <c r="N7">
+        <v>115</v>
+      </c>
+      <c r="O7">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P7">
+        <v>113.8</v>
+      </c>
+      <c r="Q7">
+        <v>104.04</v>
+      </c>
+      <c r="R7">
+        <v>95.68</v>
+      </c>
+      <c r="S7">
+        <v>88.61</v>
+      </c>
+      <c r="T7">
+        <v>82.05</v>
+      </c>
+      <c r="U7">
+        <v>75.05</v>
+      </c>
+      <c r="V7">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="W7">
+        <v>62.21</v>
+      </c>
+      <c r="X7">
+        <v>56.34</v>
+      </c>
+      <c r="Y7">
+        <v>50.7</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
@@ -8122,8 +9896,44 @@
       <c r="L8">
         <v>56.43</v>
       </c>
+      <c r="N8">
+        <v>120</v>
+      </c>
+      <c r="O8">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P8">
+        <v>109.9</v>
+      </c>
+      <c r="Q8">
+        <v>98.36</v>
+      </c>
+      <c r="R8">
+        <v>88.47</v>
+      </c>
+      <c r="S8">
+        <v>80.11</v>
+      </c>
+      <c r="T8">
+        <v>72.349999999999994</v>
+      </c>
+      <c r="U8">
+        <v>64.06</v>
+      </c>
+      <c r="V8">
+        <v>56.2</v>
+      </c>
+      <c r="W8">
+        <v>48.87</v>
+      </c>
+      <c r="X8">
+        <v>41.93</v>
+      </c>
+      <c r="Y8">
+        <v>35.25</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>125</v>
       </c>
@@ -8160,8 +9970,44 @@
       <c r="L9">
         <v>46.51</v>
       </c>
+      <c r="N9">
+        <v>125</v>
+      </c>
+      <c r="O9">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P9">
+        <v>106.2</v>
+      </c>
+      <c r="Q9">
+        <v>92.97</v>
+      </c>
+      <c r="R9">
+        <v>81.62</v>
+      </c>
+      <c r="S9">
+        <v>72.03</v>
+      </c>
+      <c r="T9">
+        <v>63.12</v>
+      </c>
+      <c r="U9">
+        <v>53.62</v>
+      </c>
+      <c r="V9">
+        <v>44.6</v>
+      </c>
+      <c r="W9">
+        <v>36.19</v>
+      </c>
+      <c r="X9">
+        <v>28.23</v>
+      </c>
+      <c r="Y9">
+        <v>20.57</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>130</v>
       </c>
@@ -8198,8 +10044,44 @@
       <c r="L10">
         <v>36.93</v>
       </c>
+      <c r="N10">
+        <v>130</v>
+      </c>
+      <c r="O10">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P10">
+        <v>102.72</v>
+      </c>
+      <c r="Q10">
+        <v>87.89</v>
+      </c>
+      <c r="R10">
+        <v>75.17</v>
+      </c>
+      <c r="S10">
+        <v>64.42</v>
+      </c>
+      <c r="T10">
+        <v>54.44</v>
+      </c>
+      <c r="U10">
+        <v>43.79</v>
+      </c>
+      <c r="V10">
+        <v>33.68</v>
+      </c>
+      <c r="W10">
+        <v>24.26</v>
+      </c>
+      <c r="X10">
+        <v>15.34</v>
+      </c>
+      <c r="Y10">
+        <v>6.75</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>135</v>
       </c>
@@ -8236,8 +10118,44 @@
       <c r="L11">
         <v>27.68</v>
       </c>
+      <c r="N11">
+        <v>135</v>
+      </c>
+      <c r="O11">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P11">
+        <v>99.49</v>
+      </c>
+      <c r="Q11">
+        <v>83.17</v>
+      </c>
+      <c r="R11">
+        <v>69.180000000000007</v>
+      </c>
+      <c r="S11">
+        <v>57.36</v>
+      </c>
+      <c r="T11">
+        <v>46.37</v>
+      </c>
+      <c r="U11">
+        <v>34.659999999999997</v>
+      </c>
+      <c r="V11">
+        <v>23.54</v>
+      </c>
+      <c r="W11">
+        <v>13.17</v>
+      </c>
+      <c r="X11">
+        <v>3.36</v>
+      </c>
+      <c r="Y11">
+        <v>-6.09</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>140</v>
       </c>
@@ -8274,8 +10192,44 @@
       <c r="L12">
         <v>18.739999999999998</v>
       </c>
+      <c r="N12">
+        <v>140</v>
+      </c>
+      <c r="O12">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P12">
+        <v>96.52</v>
+      </c>
+      <c r="Q12">
+        <v>78.84</v>
+      </c>
+      <c r="R12">
+        <v>63.69</v>
+      </c>
+      <c r="S12">
+        <v>50.88</v>
+      </c>
+      <c r="T12">
+        <v>38.979999999999997</v>
+      </c>
+      <c r="U12">
+        <v>26.29</v>
+      </c>
+      <c r="V12">
+        <v>14.25</v>
+      </c>
+      <c r="W12">
+        <v>3.02</v>
+      </c>
+      <c r="X12">
+        <v>-7.62</v>
+      </c>
+      <c r="Y12">
+        <v>-17.850000000000001</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>145</v>
       </c>
@@ -8312,8 +10266,44 @@
       <c r="L13">
         <v>9.64</v>
       </c>
+      <c r="N13">
+        <v>145</v>
+      </c>
+      <c r="O13">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P13">
+        <v>93.85</v>
+      </c>
+      <c r="Q13">
+        <v>74.95</v>
+      </c>
+      <c r="R13">
+        <v>58.74</v>
+      </c>
+      <c r="S13">
+        <v>45.05</v>
+      </c>
+      <c r="T13">
+        <v>32.32</v>
+      </c>
+      <c r="U13">
+        <v>18.75</v>
+      </c>
+      <c r="V13">
+        <v>5.87</v>
+      </c>
+      <c r="W13">
+        <v>-6.14</v>
+      </c>
+      <c r="X13">
+        <v>-17.510000000000002</v>
+      </c>
+      <c r="Y13">
+        <v>-28.45</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>150</v>
       </c>
@@ -8350,8 +10340,44 @@
       <c r="L14">
         <v>0.36</v>
       </c>
+      <c r="N14">
+        <v>150</v>
+      </c>
+      <c r="O14">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P14">
+        <v>91.5</v>
+      </c>
+      <c r="Q14">
+        <v>71.510000000000005</v>
+      </c>
+      <c r="R14">
+        <v>54.37</v>
+      </c>
+      <c r="S14">
+        <v>39.9</v>
+      </c>
+      <c r="T14">
+        <v>26.45</v>
+      </c>
+      <c r="U14">
+        <v>12.1</v>
+      </c>
+      <c r="V14">
+        <v>-1.52</v>
+      </c>
+      <c r="W14">
+        <v>-14.22</v>
+      </c>
+      <c r="X14">
+        <v>-26.24</v>
+      </c>
+      <c r="Y14">
+        <v>-37.81</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>155</v>
       </c>
@@ -8388,8 +10414,44 @@
       <c r="L15">
         <v>-7.86</v>
       </c>
+      <c r="N15">
+        <v>155</v>
+      </c>
+      <c r="O15">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P15">
+        <v>89.47</v>
+      </c>
+      <c r="Q15">
+        <v>68.55</v>
+      </c>
+      <c r="R15">
+        <v>50.62</v>
+      </c>
+      <c r="S15">
+        <v>35.47</v>
+      </c>
+      <c r="T15">
+        <v>21.39</v>
+      </c>
+      <c r="U15">
+        <v>6.38</v>
+      </c>
+      <c r="V15">
+        <v>-7.87</v>
+      </c>
+      <c r="W15">
+        <v>-21.16</v>
+      </c>
+      <c r="X15">
+        <v>-33.74</v>
+      </c>
+      <c r="Y15">
+        <v>-45.85</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>160</v>
       </c>
@@ -8426,8 +10488,44 @@
       <c r="L16">
         <v>-14.87</v>
       </c>
+      <c r="N16">
+        <v>160</v>
+      </c>
+      <c r="O16">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P16">
+        <v>87.79</v>
+      </c>
+      <c r="Q16">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="R16">
+        <v>47.51</v>
+      </c>
+      <c r="S16">
+        <v>31.8</v>
+      </c>
+      <c r="T16">
+        <v>17.21</v>
+      </c>
+      <c r="U16">
+        <v>1.64</v>
+      </c>
+      <c r="V16">
+        <v>-13.14</v>
+      </c>
+      <c r="W16">
+        <v>-26.91</v>
+      </c>
+      <c r="X16">
+        <v>-39.96</v>
+      </c>
+      <c r="Y16">
+        <v>-52.51</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>165</v>
       </c>
@@ -8464,8 +10562,44 @@
       <c r="L17">
         <v>-20.56</v>
       </c>
+      <c r="N17">
+        <v>165</v>
+      </c>
+      <c r="O17">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P17">
+        <v>86.47</v>
+      </c>
+      <c r="Q17">
+        <v>64.180000000000007</v>
+      </c>
+      <c r="R17">
+        <v>45.07</v>
+      </c>
+      <c r="S17">
+        <v>28.92</v>
+      </c>
+      <c r="T17">
+        <v>13.92</v>
+      </c>
+      <c r="U17">
+        <v>-2.09</v>
+      </c>
+      <c r="V17">
+        <v>-17.27</v>
+      </c>
+      <c r="W17">
+        <v>-31.44</v>
+      </c>
+      <c r="X17">
+        <v>-44.85</v>
+      </c>
+      <c r="Y17">
+        <v>-57.75</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>170</v>
       </c>
@@ -8502,8 +10636,44 @@
       <c r="L18">
         <v>-24.49</v>
       </c>
+      <c r="N18">
+        <v>170</v>
+      </c>
+      <c r="O18">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P18">
+        <v>85.52</v>
+      </c>
+      <c r="Q18">
+        <v>62.79</v>
+      </c>
+      <c r="R18">
+        <v>43.31</v>
+      </c>
+      <c r="S18">
+        <v>26.85</v>
+      </c>
+      <c r="T18">
+        <v>11.55</v>
+      </c>
+      <c r="U18">
+        <v>-4.7699999999999996</v>
+      </c>
+      <c r="V18">
+        <v>-20.25</v>
+      </c>
+      <c r="W18">
+        <v>-34.69</v>
+      </c>
+      <c r="X18">
+        <v>-48.36</v>
+      </c>
+      <c r="Y18">
+        <v>-61.52</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>175</v>
       </c>
@@ -8540,8 +10710,44 @@
       <c r="L19">
         <v>-26.84</v>
       </c>
+      <c r="N19">
+        <v>175</v>
+      </c>
+      <c r="O19">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P19">
+        <v>84.95</v>
+      </c>
+      <c r="Q19">
+        <v>61.96</v>
+      </c>
+      <c r="R19">
+        <v>42.25</v>
+      </c>
+      <c r="S19">
+        <v>25.6</v>
+      </c>
+      <c r="T19">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="U19">
+        <v>-6.38</v>
+      </c>
+      <c r="V19">
+        <v>-22.05</v>
+      </c>
+      <c r="W19">
+        <v>-36.65</v>
+      </c>
+      <c r="X19">
+        <v>-50.48</v>
+      </c>
+      <c r="Y19">
+        <v>-63.79</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>180</v>
       </c>
@@ -8578,8 +10784,44 @@
       <c r="L20">
         <v>-27.64</v>
       </c>
+      <c r="N20">
+        <v>180</v>
+      </c>
+      <c r="O20">
+        <v>135.05000000000001</v>
+      </c>
+      <c r="P20">
+        <v>84.76</v>
+      </c>
+      <c r="Q20">
+        <v>61.68</v>
+      </c>
+      <c r="R20">
+        <v>41.89</v>
+      </c>
+      <c r="S20">
+        <v>25.18</v>
+      </c>
+      <c r="T20">
+        <v>9.65</v>
+      </c>
+      <c r="U20">
+        <v>-6.92</v>
+      </c>
+      <c r="V20">
+        <v>-22.65</v>
+      </c>
+      <c r="W20">
+        <v>-37.31</v>
+      </c>
+      <c r="X20">
+        <v>-51.19</v>
+      </c>
+      <c r="Y20">
+        <v>-64.55</v>
+      </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -8614,7 +10856,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>90</v>
       </c>
@@ -8652,7 +10894,7 @@
         <v>122.91</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>95</v>
       </c>
@@ -8690,7 +10932,7 @@
         <v>113.96</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>100</v>
       </c>
@@ -8728,7 +10970,7 @@
         <v>105.1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>105</v>
       </c>
@@ -8766,7 +11008,7 @@
         <v>95.79</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>110</v>
       </c>
@@ -8804,7 +11046,7 @@
         <v>86.04</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>115</v>
       </c>
@@ -8842,7 +11084,7 @@
         <v>76.37</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>120</v>
       </c>
@@ -8880,7 +11122,7 @@
         <v>66.78</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>125</v>
       </c>
@@ -8918,7 +11160,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>130</v>
       </c>
@@ -8956,7 +11198,7 @@
         <v>47.53</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>135</v>
       </c>
@@ -9345,10 +11587,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9385,8 +11627,44 @@
       <c r="L1">
         <v>340</v>
       </c>
+      <c r="N1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <v>34</v>
+      </c>
+      <c r="Q1">
+        <v>68</v>
+      </c>
+      <c r="R1">
+        <v>102</v>
+      </c>
+      <c r="S1">
+        <v>136</v>
+      </c>
+      <c r="T1">
+        <v>170</v>
+      </c>
+      <c r="U1">
+        <v>204</v>
+      </c>
+      <c r="V1">
+        <v>238</v>
+      </c>
+      <c r="W1">
+        <v>272</v>
+      </c>
+      <c r="X1">
+        <v>306</v>
+      </c>
+      <c r="Y1">
+        <v>340</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
@@ -9423,8 +11701,44 @@
       <c r="L2">
         <v>246.89</v>
       </c>
+      <c r="N2">
+        <v>90</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>51.6</v>
+      </c>
+      <c r="Q2">
+        <v>86.27</v>
+      </c>
+      <c r="R2">
+        <v>116.55</v>
+      </c>
+      <c r="S2">
+        <v>144.27000000000001</v>
+      </c>
+      <c r="T2">
+        <v>168.9</v>
+      </c>
+      <c r="U2">
+        <v>190</v>
+      </c>
+      <c r="V2">
+        <v>207.22</v>
+      </c>
+      <c r="W2">
+        <v>222.05</v>
+      </c>
+      <c r="X2">
+        <v>235.76</v>
+      </c>
+      <c r="Y2">
+        <v>248.75</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
@@ -9461,8 +11775,44 @@
       <c r="L3">
         <v>248.04</v>
       </c>
+      <c r="N3">
+        <v>95</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>51.4</v>
+      </c>
+      <c r="Q3">
+        <v>85.94</v>
+      </c>
+      <c r="R3">
+        <v>116.1</v>
+      </c>
+      <c r="S3">
+        <v>143.72</v>
+      </c>
+      <c r="T3">
+        <v>168.25</v>
+      </c>
+      <c r="U3">
+        <v>189.28</v>
+      </c>
+      <c r="V3">
+        <v>206.43</v>
+      </c>
+      <c r="W3">
+        <v>221.21</v>
+      </c>
+      <c r="X3">
+        <v>234.87</v>
+      </c>
+      <c r="Y3">
+        <v>247.81</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -9499,8 +11849,44 @@
       <c r="L4">
         <v>248.29</v>
       </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>50.81</v>
+      </c>
+      <c r="Q4">
+        <v>84.96</v>
+      </c>
+      <c r="R4">
+        <v>114.78</v>
+      </c>
+      <c r="S4">
+        <v>142.07</v>
+      </c>
+      <c r="T4">
+        <v>166.33</v>
+      </c>
+      <c r="U4">
+        <v>187.11</v>
+      </c>
+      <c r="V4">
+        <v>204.07</v>
+      </c>
+      <c r="W4">
+        <v>218.68</v>
+      </c>
+      <c r="X4">
+        <v>232.18</v>
+      </c>
+      <c r="Y4">
+        <v>244.97</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
@@ -9537,8 +11923,44 @@
       <c r="L5">
         <v>247.56</v>
       </c>
+      <c r="N5">
+        <v>105</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>49.84</v>
+      </c>
+      <c r="Q5">
+        <v>83.33</v>
+      </c>
+      <c r="R5">
+        <v>112.58</v>
+      </c>
+      <c r="S5">
+        <v>139.35</v>
+      </c>
+      <c r="T5">
+        <v>163.13999999999999</v>
+      </c>
+      <c r="U5">
+        <v>183.53</v>
+      </c>
+      <c r="V5">
+        <v>200.16</v>
+      </c>
+      <c r="W5">
+        <v>214.49</v>
+      </c>
+      <c r="X5">
+        <v>227.73</v>
+      </c>
+      <c r="Y5">
+        <v>240.28</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
@@ -9575,8 +11997,44 @@
       <c r="L6">
         <v>245.81</v>
       </c>
+      <c r="N6">
+        <v>110</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>48.48</v>
+      </c>
+      <c r="Q6">
+        <v>81.069999999999993</v>
+      </c>
+      <c r="R6">
+        <v>109.52</v>
+      </c>
+      <c r="S6">
+        <v>135.57</v>
+      </c>
+      <c r="T6">
+        <v>158.71</v>
+      </c>
+      <c r="U6">
+        <v>178.54</v>
+      </c>
+      <c r="V6">
+        <v>194.72</v>
+      </c>
+      <c r="W6">
+        <v>208.66</v>
+      </c>
+      <c r="X6">
+        <v>221.55</v>
+      </c>
+      <c r="Y6">
+        <v>233.75</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
@@ -9613,8 +12071,44 @@
       <c r="L7">
         <v>242.94</v>
       </c>
+      <c r="N7">
+        <v>115</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>46.76</v>
+      </c>
+      <c r="Q7">
+        <v>78.19</v>
+      </c>
+      <c r="R7">
+        <v>105.63</v>
+      </c>
+      <c r="S7">
+        <v>130.75</v>
+      </c>
+      <c r="T7">
+        <v>153.07</v>
+      </c>
+      <c r="U7">
+        <v>172.2</v>
+      </c>
+      <c r="V7">
+        <v>187.8</v>
+      </c>
+      <c r="W7">
+        <v>201.25</v>
+      </c>
+      <c r="X7">
+        <v>213.68</v>
+      </c>
+      <c r="Y7">
+        <v>225.45</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
@@ -9651,8 +12145,44 @@
       <c r="L8">
         <v>238.77</v>
       </c>
+      <c r="N8">
+        <v>120</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>44.68</v>
+      </c>
+      <c r="Q8">
+        <v>74.709999999999994</v>
+      </c>
+      <c r="R8">
+        <v>100.93</v>
+      </c>
+      <c r="S8">
+        <v>124.94</v>
+      </c>
+      <c r="T8">
+        <v>146.27000000000001</v>
+      </c>
+      <c r="U8">
+        <v>164.55</v>
+      </c>
+      <c r="V8">
+        <v>179.46</v>
+      </c>
+      <c r="W8">
+        <v>192.3</v>
+      </c>
+      <c r="X8">
+        <v>204.18</v>
+      </c>
+      <c r="Y8">
+        <v>215.43</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>125</v>
       </c>
@@ -9689,8 +12219,44 @@
       <c r="L9">
         <v>233.16</v>
       </c>
+      <c r="N9">
+        <v>125</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>42.26</v>
+      </c>
+      <c r="Q9">
+        <v>70.67</v>
+      </c>
+      <c r="R9">
+        <v>95.47</v>
+      </c>
+      <c r="S9">
+        <v>118.18</v>
+      </c>
+      <c r="T9">
+        <v>138.35</v>
+      </c>
+      <c r="U9">
+        <v>155.63999999999999</v>
+      </c>
+      <c r="V9">
+        <v>169.74</v>
+      </c>
+      <c r="W9">
+        <v>181.9</v>
+      </c>
+      <c r="X9">
+        <v>193.13</v>
+      </c>
+      <c r="Y9">
+        <v>203.77</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>130</v>
       </c>
@@ -9727,8 +12293,44 @@
       <c r="L10">
         <v>226.02</v>
       </c>
+      <c r="N10">
+        <v>130</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="Q10">
+        <v>66.09</v>
+      </c>
+      <c r="R10">
+        <v>89.28</v>
+      </c>
+      <c r="S10">
+        <v>110.52</v>
+      </c>
+      <c r="T10">
+        <v>129.38999999999999</v>
+      </c>
+      <c r="U10">
+        <v>145.55000000000001</v>
+      </c>
+      <c r="V10">
+        <v>158.74</v>
+      </c>
+      <c r="W10">
+        <v>170.1</v>
+      </c>
+      <c r="X10">
+        <v>180.61</v>
+      </c>
+      <c r="Y10">
+        <v>190.56</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>135</v>
       </c>
@@ -9765,8 +12367,44 @@
       <c r="L11">
         <v>217.23</v>
       </c>
+      <c r="N11">
+        <v>135</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="Q11">
+        <v>61</v>
+      </c>
+      <c r="R11">
+        <v>82.41</v>
+      </c>
+      <c r="S11">
+        <v>102.01</v>
+      </c>
+      <c r="T11">
+        <v>119.43</v>
+      </c>
+      <c r="U11">
+        <v>134.35</v>
+      </c>
+      <c r="V11">
+        <v>146.53</v>
+      </c>
+      <c r="W11">
+        <v>157.02000000000001</v>
+      </c>
+      <c r="X11">
+        <v>166.71</v>
+      </c>
+      <c r="Y11">
+        <v>175.9</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>140</v>
       </c>
@@ -9803,8 +12441,44 @@
       <c r="L12">
         <v>206.4</v>
       </c>
+      <c r="N12">
+        <v>140</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>33.17</v>
+      </c>
+      <c r="Q12">
+        <v>55.46</v>
+      </c>
+      <c r="R12">
+        <v>74.92</v>
+      </c>
+      <c r="S12">
+        <v>92.74</v>
+      </c>
+      <c r="T12">
+        <v>108.57</v>
+      </c>
+      <c r="U12">
+        <v>122.13</v>
+      </c>
+      <c r="V12">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="W12">
+        <v>142.72999999999999</v>
+      </c>
+      <c r="X12">
+        <v>151.55000000000001</v>
+      </c>
+      <c r="Y12">
+        <v>159.9</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>145</v>
       </c>
@@ -9841,8 +12515,44 @@
       <c r="L13">
         <v>192.03</v>
       </c>
+      <c r="N13">
+        <v>145</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>29.59</v>
+      </c>
+      <c r="Q13">
+        <v>49.48</v>
+      </c>
+      <c r="R13">
+        <v>66.849999999999994</v>
+      </c>
+      <c r="S13">
+        <v>82.75</v>
+      </c>
+      <c r="T13">
+        <v>96.88</v>
+      </c>
+      <c r="U13">
+        <v>108.98</v>
+      </c>
+      <c r="V13">
+        <v>118.86</v>
+      </c>
+      <c r="W13">
+        <v>127.37</v>
+      </c>
+      <c r="X13">
+        <v>135.22999999999999</v>
+      </c>
+      <c r="Y13">
+        <v>142.68</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>150</v>
       </c>
@@ -9879,8 +12589,44 @@
       <c r="L14">
         <v>173.53</v>
       </c>
+      <c r="N14">
+        <v>150</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>25.8</v>
+      </c>
+      <c r="Q14">
+        <v>43.14</v>
+      </c>
+      <c r="R14">
+        <v>58.28</v>
+      </c>
+      <c r="S14">
+        <v>72.14</v>
+      </c>
+      <c r="T14">
+        <v>84.45</v>
+      </c>
+      <c r="U14">
+        <v>95</v>
+      </c>
+      <c r="V14">
+        <v>103.61</v>
+      </c>
+      <c r="W14">
+        <v>111.03</v>
+      </c>
+      <c r="X14">
+        <v>117.88</v>
+      </c>
+      <c r="Y14">
+        <v>124.38</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>155</v>
       </c>
@@ -9917,8 +12663,44 @@
       <c r="L15">
         <v>153.05000000000001</v>
       </c>
+      <c r="N15">
+        <v>155</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>21.81</v>
+      </c>
+      <c r="Q15">
+        <v>36.46</v>
+      </c>
+      <c r="R15">
+        <v>49.26</v>
+      </c>
+      <c r="S15">
+        <v>60.97</v>
+      </c>
+      <c r="T15">
+        <v>71.38</v>
+      </c>
+      <c r="U15">
+        <v>80.3</v>
+      </c>
+      <c r="V15">
+        <v>87.58</v>
+      </c>
+      <c r="W15">
+        <v>93.85</v>
+      </c>
+      <c r="X15">
+        <v>99.64</v>
+      </c>
+      <c r="Y15">
+        <v>105.13</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>160</v>
       </c>
@@ -9955,8 +12737,44 @@
       <c r="L16">
         <v>129.46</v>
       </c>
+      <c r="N16">
+        <v>160</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="Q16">
+        <v>29.51</v>
+      </c>
+      <c r="R16">
+        <v>39.86</v>
+      </c>
+      <c r="S16">
+        <v>49.35</v>
+      </c>
+      <c r="T16">
+        <v>57.77</v>
+      </c>
+      <c r="U16">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="V16">
+        <v>70.87</v>
+      </c>
+      <c r="W16">
+        <v>75.95</v>
+      </c>
+      <c r="X16">
+        <v>80.64</v>
+      </c>
+      <c r="Y16">
+        <v>85.08</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>165</v>
       </c>
@@ -9993,8 +12811,44 @@
       <c r="L17">
         <v>101.48</v>
       </c>
+      <c r="N17">
+        <v>165</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>13.35</v>
+      </c>
+      <c r="Q17">
+        <v>22.33</v>
+      </c>
+      <c r="R17">
+        <v>30.17</v>
+      </c>
+      <c r="S17">
+        <v>37.340000000000003</v>
+      </c>
+      <c r="T17">
+        <v>43.72</v>
+      </c>
+      <c r="U17">
+        <v>49.18</v>
+      </c>
+      <c r="V17">
+        <v>53.63</v>
+      </c>
+      <c r="W17">
+        <v>57.47</v>
+      </c>
+      <c r="X17">
+        <v>61.02</v>
+      </c>
+      <c r="Y17">
+        <v>64.38</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>170</v>
       </c>
@@ -10031,8 +12885,44 @@
       <c r="L18">
         <v>69.459999999999994</v>
       </c>
+      <c r="N18">
+        <v>170</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="Q18">
+        <v>14.98</v>
+      </c>
+      <c r="R18">
+        <v>20.239999999999998</v>
+      </c>
+      <c r="S18">
+        <v>25.06</v>
+      </c>
+      <c r="T18">
+        <v>29.33</v>
+      </c>
+      <c r="U18">
+        <v>33</v>
+      </c>
+      <c r="V18">
+        <v>35.99</v>
+      </c>
+      <c r="W18">
+        <v>38.56</v>
+      </c>
+      <c r="X18">
+        <v>40.94</v>
+      </c>
+      <c r="Y18">
+        <v>43.2</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>175</v>
       </c>
@@ -10069,8 +12959,44 @@
       <c r="L19">
         <v>35.14</v>
       </c>
+      <c r="N19">
+        <v>175</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>4.5</v>
+      </c>
+      <c r="Q19">
+        <v>7.52</v>
+      </c>
+      <c r="R19">
+        <v>10.16</v>
+      </c>
+      <c r="S19">
+        <v>12.58</v>
+      </c>
+      <c r="T19">
+        <v>14.72</v>
+      </c>
+      <c r="U19">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="V19">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="W19">
+        <v>19.36</v>
+      </c>
+      <c r="X19">
+        <v>20.55</v>
+      </c>
+      <c r="Y19">
+        <v>21.68</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>180</v>
       </c>
@@ -10107,8 +13033,44 @@
       <c r="L20">
         <v>-0.03</v>
       </c>
+      <c r="N20">
+        <v>180</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -10143,7 +13105,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>90</v>
       </c>
@@ -10181,7 +13143,7 @@
         <v>263.44</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>95</v>
       </c>
@@ -10219,7 +13181,7 @@
         <v>261.91000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>100</v>
       </c>
@@ -10257,7 +13219,7 @@
         <v>260.39</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>105</v>
       </c>
@@ -10295,7 +13257,7 @@
         <v>258.88</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>110</v>
       </c>
@@ -10333,7 +13295,7 @@
         <v>255.29</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>115</v>
       </c>
@@ -10371,7 +13333,7 @@
         <v>250.66</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>120</v>
       </c>
@@ -10409,7 +13371,7 @@
         <v>246.07</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>125</v>
       </c>
@@ -10447,7 +13409,7 @@
         <v>239.41</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>130</v>
       </c>
@@ -10485,7 +13447,7 @@
         <v>232.33</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>135</v>
       </c>

--- a/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
+++ b/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
@@ -1232,61 +1232,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>135.66999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>130.66999999999999</c:v>
+                  <c:v>134.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>126.32</c:v>
+                  <c:v>132.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>122.03</c:v>
+                  <c:v>131.16999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>117.85</c:v>
+                  <c:v>129.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>113.8</c:v>
+                  <c:v>128.32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>109.9</c:v>
+                  <c:v>126.97</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>106.2</c:v>
+                  <c:v>125.69</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>102.72</c:v>
+                  <c:v>124.48</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>99.49</c:v>
+                  <c:v>123.36</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.52</c:v>
+                  <c:v>122.33</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>93.85</c:v>
+                  <c:v>121.41</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>91.5</c:v>
+                  <c:v>120.59</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>89.47</c:v>
+                  <c:v>119.89</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>87.79</c:v>
+                  <c:v>119.31</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>86.47</c:v>
+                  <c:v>118.85</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>85.52</c:v>
+                  <c:v>118.52</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>84.95</c:v>
+                  <c:v>118.32</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>84.76</c:v>
+                  <c:v>118.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1315,61 +1315,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>119.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>117.66</c:v>
+                  <c:v>109.84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100.39</c:v>
+                  <c:v>99.45</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83.39</c:v>
+                  <c:v>88.64</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66.790000000000006</c:v>
+                  <c:v>77.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.7</c:v>
+                  <c:v>67.31</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.25</c:v>
+                  <c:v>57.07</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.57</c:v>
+                  <c:v>47.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.75</c:v>
+                  <c:v>37.58</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-6.09</c:v>
+                  <c:v>28.34</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-17.850000000000001</c:v>
+                  <c:v>19.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-28.45</c:v>
+                  <c:v>10.32</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-37.81</c:v>
+                  <c:v>1.05</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-45.85</c:v>
+                  <c:v>-7.16</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-52.51</c:v>
+                  <c:v>-14.17</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-57.75</c:v>
+                  <c:v>-19.86</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-61.52</c:v>
+                  <c:v>-23.78</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-63.79</c:v>
+                  <c:v>-26.12</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-64.55</c:v>
+                  <c:v>-26.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1385,11 +1385,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-74225200"/>
-        <c:axId val="-74234448"/>
+        <c:axId val="-580418848"/>
+        <c:axId val="-580425920"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-74225200"/>
+        <c:axId val="-580418848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1432,7 +1432,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74234448"/>
+        <c:crossAx val="-580425920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1440,7 +1440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-74234448"/>
+        <c:axId val="-580425920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1491,7 +1491,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74225200"/>
+        <c:crossAx val="-580418848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1774,7 +1774,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$B$23:$L$23</c:f>
+              <c:f>Lambda_d_matrix!$B$24:$L$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1782,34 +1782,34 @@
                   <c:v>135.87</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>142.15</c:v>
+                  <c:v>140.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>141.69</c:v>
+                  <c:v>138.44999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139.61000000000001</c:v>
+                  <c:v>136.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>137.36000000000001</c:v>
+                  <c:v>133.34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>135.22</c:v>
+                  <c:v>129.97</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>132.78</c:v>
+                  <c:v>126.61</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>130.58000000000001</c:v>
+                  <c:v>123.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>128.37</c:v>
+                  <c:v>120.47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>125.11</c:v>
+                  <c:v>117.21</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>122.91</c:v>
+                  <c:v>113.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1886,42 +1886,42 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$O$2:$Y$2</c:f>
+              <c:f>Lambda_d_matrix!$O$3:$Y$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>135.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>134.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>132.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>130.69999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>127.54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>123.92</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>120.71</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>117.96</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>115.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>112.58</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>109.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2227,37 +2227,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.05000000000001</c:v>
+                  <c:v>135.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>84.76</c:v>
+                  <c:v>118.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61.68</c:v>
+                  <c:v>100.85</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.89</c:v>
+                  <c:v>83.67</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25.18</c:v>
+                  <c:v>67.14</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.65</c:v>
+                  <c:v>50.99</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-6.92</c:v>
+                  <c:v>35.049999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-22.65</c:v>
+                  <c:v>19.29</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-37.31</c:v>
+                  <c:v>3.71</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-51.19</c:v>
+                  <c:v>-11.71</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-64.55</c:v>
+                  <c:v>-26.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,11 +2273,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-148748112"/>
-        <c:axId val="-148751920"/>
+        <c:axId val="-580431360"/>
+        <c:axId val="-580419392"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-148748112"/>
+        <c:axId val="-580431360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2320,7 +2320,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-148751920"/>
+        <c:crossAx val="-580419392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2328,7 +2328,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-148751920"/>
+        <c:axId val="-580419392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2379,7 +2379,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-148748112"/>
+        <c:crossAx val="-580431360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2979,37 +2979,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51.6</c:v>
+                  <c:v>44.53</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>86.27</c:v>
+                  <c:v>88.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>116.55</c:v>
+                  <c:v>127.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>144.27000000000001</c:v>
+                  <c:v>156.63999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>168.9</c:v>
+                  <c:v>178.99</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>190</c:v>
+                  <c:v>197</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>207.22</c:v>
+                  <c:v>211.64</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>222.05</c:v>
+                  <c:v>224.47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>235.76</c:v>
+                  <c:v>236</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>248.75</c:v>
+                  <c:v>246.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3091,37 +3091,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5</c:v>
+                  <c:v>3.85</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.52</c:v>
+                  <c:v>7.71</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.16</c:v>
+                  <c:v>11.51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.58</c:v>
+                  <c:v>15.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.72</c:v>
+                  <c:v>18.88</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16.559999999999999</c:v>
+                  <c:v>22.41</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.059999999999999</c:v>
+                  <c:v>25.76</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.36</c:v>
+                  <c:v>28.98</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20.55</c:v>
+                  <c:v>32.090000000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21.68</c:v>
+                  <c:v>35.119999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3137,11 +3137,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-74236624"/>
-        <c:axId val="-74233360"/>
+        <c:axId val="-580429728"/>
+        <c:axId val="-580423744"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-74236624"/>
+        <c:axId val="-580429728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3184,7 +3184,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74233360"/>
+        <c:crossAx val="-580423744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3192,7 +3192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-74233360"/>
+        <c:axId val="-580423744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3243,7 +3243,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74236624"/>
+        <c:crossAx val="-580429728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,61 +3763,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>248.75</c:v>
+                  <c:v>246.71</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>247.81</c:v>
+                  <c:v>247.87</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>244.97</c:v>
+                  <c:v>248.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240.28</c:v>
+                  <c:v>247.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>233.75</c:v>
+                  <c:v>245.65</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>225.45</c:v>
+                  <c:v>242.78</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>215.43</c:v>
+                  <c:v>238.63</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>203.77</c:v>
+                  <c:v>233.01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>190.56</c:v>
+                  <c:v>225.89</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>175.9</c:v>
+                  <c:v>217.1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>159.9</c:v>
+                  <c:v>206.28</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>142.68</c:v>
+                  <c:v>191.94</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>124.38</c:v>
+                  <c:v>173.47</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>105.13</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>85.08</c:v>
+                  <c:v>129.41</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>64.38</c:v>
+                  <c:v>101.42</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>43.2</c:v>
+                  <c:v>69.41</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.68</c:v>
+                  <c:v>35.119999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>-0.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4243,61 +4243,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>51.6</c:v>
+                  <c:v>44.53</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51.4</c:v>
+                  <c:v>44.37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.81</c:v>
+                  <c:v>43.87</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>49.84</c:v>
+                  <c:v>43.03</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>48.48</c:v>
+                  <c:v>41.86</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.76</c:v>
+                  <c:v>40.369999999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44.68</c:v>
+                  <c:v>38.57</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42.26</c:v>
+                  <c:v>36.47</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39.520000000000003</c:v>
+                  <c:v>34.090000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>36.479999999999997</c:v>
+                  <c:v>31.45</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>33.17</c:v>
+                  <c:v>28.57</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>29.59</c:v>
+                  <c:v>25.47</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>25.8</c:v>
+                  <c:v>22.19</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21.81</c:v>
+                  <c:v>18.739999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>17.649999999999999</c:v>
+                  <c:v>15.16</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13.35</c:v>
+                  <c:v>11.46</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.9600000000000009</c:v>
+                  <c:v>7.68</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.5</c:v>
+                  <c:v>3.85</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>-0.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4313,11 +4313,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-67944288"/>
-        <c:axId val="-67939936"/>
+        <c:axId val="-580418304"/>
+        <c:axId val="-580427552"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-67944288"/>
+        <c:axId val="-580418304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4360,7 +4360,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-67939936"/>
+        <c:crossAx val="-580427552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4368,7 +4368,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-67939936"/>
+        <c:axId val="-580427552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4419,7 +4419,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-67944288"/>
+        <c:crossAx val="-580418304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4925,11 +4925,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-74234992"/>
-        <c:axId val="-74232816"/>
+        <c:axId val="-580416672"/>
+        <c:axId val="-580429184"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-74234992"/>
+        <c:axId val="-580416672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4971,7 +4971,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74232816"/>
+        <c:crossAx val="-580429184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4979,7 +4979,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-74232816"/>
+        <c:axId val="-580429184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5030,7 +5030,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74234992"/>
+        <c:crossAx val="-580416672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5388,11 +5388,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-74231728"/>
-        <c:axId val="-74231184"/>
+        <c:axId val="-580428640"/>
+        <c:axId val="-580427008"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-74231728"/>
+        <c:axId val="-580428640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5434,7 +5434,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74231184"/>
+        <c:crossAx val="-580427008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5442,7 +5442,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-74231184"/>
+        <c:axId val="-580427008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5493,7 +5493,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-74231728"/>
+        <c:crossAx val="-580428640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9456,37 +9456,37 @@
         <v>90</v>
       </c>
       <c r="O2">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P2">
-        <v>135.05000000000001</v>
+        <v>135.66999999999999</v>
       </c>
       <c r="Q2">
-        <v>135.05000000000001</v>
+        <v>135.6</v>
       </c>
       <c r="R2">
-        <v>135.05000000000001</v>
+        <v>134.72</v>
       </c>
       <c r="S2">
-        <v>135.05000000000001</v>
+        <v>132.47999999999999</v>
       </c>
       <c r="T2">
-        <v>135.05000000000001</v>
+        <v>129.72999999999999</v>
       </c>
       <c r="U2">
-        <v>135.05000000000001</v>
+        <v>127.23</v>
       </c>
       <c r="V2">
-        <v>135.05000000000001</v>
+        <v>125.26</v>
       </c>
       <c r="W2">
-        <v>135.05000000000001</v>
+        <v>123.41</v>
       </c>
       <c r="X2">
-        <v>135.05000000000001</v>
+        <v>121.57</v>
       </c>
       <c r="Y2">
-        <v>135.05000000000001</v>
+        <v>119.74</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -9530,37 +9530,37 @@
         <v>95</v>
       </c>
       <c r="O3">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P3">
-        <v>130.66999999999999</v>
+        <v>134.16</v>
       </c>
       <c r="Q3">
-        <v>128.65</v>
+        <v>132.65</v>
       </c>
       <c r="R3">
-        <v>126.93</v>
+        <v>130.69999999999999</v>
       </c>
       <c r="S3">
-        <v>125.47</v>
+        <v>127.54</v>
       </c>
       <c r="T3">
-        <v>124.12</v>
+        <v>123.92</v>
       </c>
       <c r="U3">
-        <v>122.67</v>
+        <v>120.71</v>
       </c>
       <c r="V3">
-        <v>121.3</v>
+        <v>117.96</v>
       </c>
       <c r="W3">
-        <v>120.03</v>
+        <v>115.28</v>
       </c>
       <c r="X3">
-        <v>118.82</v>
+        <v>112.58</v>
       </c>
       <c r="Y3">
-        <v>117.66</v>
+        <v>109.84</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -9604,37 +9604,37 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P4">
-        <v>126.32</v>
+        <v>132.65</v>
       </c>
       <c r="Q4">
-        <v>122.31</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="R4">
-        <v>118.87</v>
+        <v>126.66</v>
       </c>
       <c r="S4">
-        <v>115.97</v>
+        <v>122.56</v>
       </c>
       <c r="T4">
-        <v>113.27</v>
+        <v>118.04</v>
       </c>
       <c r="U4">
-        <v>110.39</v>
+        <v>114.03</v>
       </c>
       <c r="V4">
-        <v>107.67</v>
+        <v>110.44</v>
       </c>
       <c r="W4">
-        <v>105.12</v>
+        <v>106.87</v>
       </c>
       <c r="X4">
-        <v>102.71</v>
+        <v>103.2</v>
       </c>
       <c r="Y4">
-        <v>100.39</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -9678,37 +9678,37 @@
         <v>105</v>
       </c>
       <c r="O5">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P5">
-        <v>122.03</v>
+        <v>131.16999999999999</v>
       </c>
       <c r="Q5">
-        <v>116.06</v>
+        <v>126.78</v>
       </c>
       <c r="R5">
-        <v>110.94</v>
+        <v>122.6</v>
       </c>
       <c r="S5">
-        <v>106.61</v>
+        <v>117.56</v>
       </c>
       <c r="T5">
-        <v>102.59</v>
+        <v>112.08</v>
       </c>
       <c r="U5">
-        <v>98.3</v>
+        <v>107.15</v>
       </c>
       <c r="V5">
-        <v>94.23</v>
+        <v>102.61</v>
       </c>
       <c r="W5">
-        <v>90.44</v>
+        <v>98.08</v>
       </c>
       <c r="X5">
-        <v>86.85</v>
+        <v>93.42</v>
       </c>
       <c r="Y5">
-        <v>83.39</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -9752,37 +9752,37 @@
         <v>110</v>
       </c>
       <c r="O6">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P6">
-        <v>117.85</v>
+        <v>129.72</v>
       </c>
       <c r="Q6">
-        <v>109.95</v>
+        <v>123.91</v>
       </c>
       <c r="R6">
-        <v>103.19</v>
+        <v>118.53</v>
       </c>
       <c r="S6">
-        <v>97.47</v>
+        <v>112.59</v>
       </c>
       <c r="T6">
-        <v>92.16</v>
+        <v>106.16</v>
       </c>
       <c r="U6">
-        <v>86.49</v>
+        <v>100.24</v>
       </c>
       <c r="V6">
-        <v>81.11</v>
+        <v>94.71</v>
       </c>
       <c r="W6">
-        <v>76.099999999999994</v>
+        <v>89.2</v>
       </c>
       <c r="X6">
-        <v>71.349999999999994</v>
+        <v>83.6</v>
       </c>
       <c r="Y6">
-        <v>66.790000000000006</v>
+        <v>77.849999999999994</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -9826,37 +9826,37 @@
         <v>115</v>
       </c>
       <c r="O7">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P7">
-        <v>113.8</v>
+        <v>128.32</v>
       </c>
       <c r="Q7">
-        <v>104.04</v>
+        <v>121.12</v>
       </c>
       <c r="R7">
-        <v>95.68</v>
+        <v>114.48</v>
       </c>
       <c r="S7">
-        <v>88.61</v>
+        <v>107.68</v>
       </c>
       <c r="T7">
-        <v>82.05</v>
+        <v>100.36</v>
       </c>
       <c r="U7">
-        <v>75.05</v>
+        <v>93.45</v>
       </c>
       <c r="V7">
-        <v>68.400000000000006</v>
+        <v>86.93</v>
       </c>
       <c r="W7">
-        <v>62.21</v>
+        <v>80.47</v>
       </c>
       <c r="X7">
-        <v>56.34</v>
+        <v>73.94</v>
       </c>
       <c r="Y7">
-        <v>50.7</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -9900,37 +9900,37 @@
         <v>120</v>
       </c>
       <c r="O8">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P8">
-        <v>109.9</v>
+        <v>126.97</v>
       </c>
       <c r="Q8">
-        <v>98.36</v>
+        <v>118.43</v>
       </c>
       <c r="R8">
-        <v>88.47</v>
+        <v>110.52</v>
       </c>
       <c r="S8">
-        <v>80.11</v>
+        <v>102.82</v>
       </c>
       <c r="T8">
-        <v>72.349999999999994</v>
+        <v>94.68</v>
       </c>
       <c r="U8">
-        <v>64.06</v>
+        <v>86.84</v>
       </c>
       <c r="V8">
-        <v>56.2</v>
+        <v>79.37</v>
       </c>
       <c r="W8">
-        <v>48.87</v>
+        <v>71.97</v>
       </c>
       <c r="X8">
-        <v>41.93</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="Y8">
-        <v>35.25</v>
+        <v>57.07</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -9974,37 +9974,37 @@
         <v>125</v>
       </c>
       <c r="O9">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P9">
-        <v>106.2</v>
+        <v>125.69</v>
       </c>
       <c r="Q9">
-        <v>92.97</v>
+        <v>115.86</v>
       </c>
       <c r="R9">
-        <v>81.62</v>
+        <v>106.7</v>
       </c>
       <c r="S9">
-        <v>72.03</v>
+        <v>97.97</v>
       </c>
       <c r="T9">
-        <v>63.12</v>
+        <v>89.12</v>
       </c>
       <c r="U9">
-        <v>53.62</v>
+        <v>80.41</v>
       </c>
       <c r="V9">
-        <v>44.6</v>
+        <v>72.05</v>
       </c>
       <c r="W9">
-        <v>36.19</v>
+        <v>63.76</v>
       </c>
       <c r="X9">
-        <v>28.23</v>
+        <v>55.46</v>
       </c>
       <c r="Y9">
-        <v>20.57</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -10048,37 +10048,37 @@
         <v>130</v>
       </c>
       <c r="O10">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P10">
-        <v>102.72</v>
+        <v>124.48</v>
       </c>
       <c r="Q10">
-        <v>87.89</v>
+        <v>113.44</v>
       </c>
       <c r="R10">
-        <v>75.17</v>
+        <v>103.06</v>
       </c>
       <c r="S10">
-        <v>64.42</v>
+        <v>93.22</v>
       </c>
       <c r="T10">
-        <v>54.44</v>
+        <v>83.59</v>
       </c>
       <c r="U10">
-        <v>43.79</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="V10">
-        <v>33.68</v>
+        <v>64.94</v>
       </c>
       <c r="W10">
-        <v>24.26</v>
+        <v>55.83</v>
       </c>
       <c r="X10">
-        <v>15.34</v>
+        <v>46.71</v>
       </c>
       <c r="Y10">
-        <v>6.75</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -10122,37 +10122,37 @@
         <v>135</v>
       </c>
       <c r="O11">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P11">
-        <v>99.49</v>
+        <v>123.36</v>
       </c>
       <c r="Q11">
-        <v>83.17</v>
+        <v>111.18</v>
       </c>
       <c r="R11">
-        <v>69.180000000000007</v>
+        <v>99.65</v>
       </c>
       <c r="S11">
-        <v>57.36</v>
+        <v>88.68</v>
       </c>
       <c r="T11">
-        <v>46.37</v>
+        <v>78.06</v>
       </c>
       <c r="U11">
-        <v>34.659999999999997</v>
+        <v>67.77</v>
       </c>
       <c r="V11">
-        <v>23.54</v>
+        <v>57.91</v>
       </c>
       <c r="W11">
-        <v>13.17</v>
+        <v>48.09</v>
       </c>
       <c r="X11">
-        <v>3.36</v>
+        <v>38.22</v>
       </c>
       <c r="Y11">
-        <v>-6.09</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -10196,37 +10196,37 @@
         <v>140</v>
       </c>
       <c r="O12">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P12">
-        <v>96.52</v>
+        <v>122.33</v>
       </c>
       <c r="Q12">
-        <v>78.84</v>
+        <v>109.1</v>
       </c>
       <c r="R12">
-        <v>63.69</v>
+        <v>96.5</v>
       </c>
       <c r="S12">
-        <v>50.88</v>
+        <v>84.44</v>
       </c>
       <c r="T12">
-        <v>38.979999999999997</v>
+        <v>72.75</v>
       </c>
       <c r="U12">
-        <v>26.29</v>
+        <v>61.44</v>
       </c>
       <c r="V12">
-        <v>14.25</v>
+        <v>50.73</v>
       </c>
       <c r="W12">
-        <v>3.02</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="X12">
-        <v>-7.62</v>
+        <v>29.9</v>
       </c>
       <c r="Y12">
-        <v>-17.850000000000001</v>
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -10270,37 +10270,37 @@
         <v>145</v>
       </c>
       <c r="O13">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P13">
-        <v>93.85</v>
+        <v>121.41</v>
       </c>
       <c r="Q13">
-        <v>74.95</v>
+        <v>107.22</v>
       </c>
       <c r="R13">
-        <v>58.74</v>
+        <v>93.62</v>
       </c>
       <c r="S13">
-        <v>45.05</v>
+        <v>80.569999999999993</v>
       </c>
       <c r="T13">
-        <v>32.32</v>
+        <v>67.87</v>
       </c>
       <c r="U13">
-        <v>18.75</v>
+        <v>55.51</v>
       </c>
       <c r="V13">
-        <v>5.87</v>
+        <v>43.66</v>
       </c>
       <c r="W13">
-        <v>-6.14</v>
+        <v>32.380000000000003</v>
       </c>
       <c r="X13">
-        <v>-17.510000000000002</v>
+        <v>21.3</v>
       </c>
       <c r="Y13">
-        <v>-28.45</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -10344,37 +10344,37 @@
         <v>150</v>
       </c>
       <c r="O14">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P14">
-        <v>91.5</v>
+        <v>120.59</v>
       </c>
       <c r="Q14">
-        <v>71.510000000000005</v>
+        <v>105.56</v>
       </c>
       <c r="R14">
-        <v>54.37</v>
+        <v>91.07</v>
       </c>
       <c r="S14">
-        <v>39.9</v>
+        <v>77.11</v>
       </c>
       <c r="T14">
-        <v>26.45</v>
+        <v>63.49</v>
       </c>
       <c r="U14">
-        <v>12.1</v>
+        <v>50.18</v>
       </c>
       <c r="V14">
-        <v>-1.52</v>
+        <v>37.25</v>
       </c>
       <c r="W14">
-        <v>-14.22</v>
+        <v>24.87</v>
       </c>
       <c r="X14">
-        <v>-26.24</v>
+        <v>12.85</v>
       </c>
       <c r="Y14">
-        <v>-37.81</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -10418,37 +10418,37 @@
         <v>155</v>
       </c>
       <c r="O15">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P15">
-        <v>89.47</v>
+        <v>119.89</v>
       </c>
       <c r="Q15">
-        <v>68.55</v>
+        <v>104.14</v>
       </c>
       <c r="R15">
-        <v>50.62</v>
+        <v>88.86</v>
       </c>
       <c r="S15">
-        <v>35.47</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="T15">
-        <v>21.39</v>
+        <v>59.69</v>
       </c>
       <c r="U15">
-        <v>6.38</v>
+        <v>45.55</v>
       </c>
       <c r="V15">
-        <v>-7.87</v>
+        <v>31.71</v>
       </c>
       <c r="W15">
-        <v>-21.16</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="X15">
-        <v>-33.74</v>
+        <v>5.41</v>
       </c>
       <c r="Y15">
-        <v>-45.85</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -10492,37 +10492,37 @@
         <v>160</v>
       </c>
       <c r="O16">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P16">
-        <v>87.79</v>
+        <v>119.31</v>
       </c>
       <c r="Q16">
-        <v>66.099999999999994</v>
+        <v>102.96</v>
       </c>
       <c r="R16">
-        <v>47.51</v>
+        <v>87.02</v>
       </c>
       <c r="S16">
-        <v>31.8</v>
+        <v>71.58</v>
       </c>
       <c r="T16">
-        <v>17.21</v>
+        <v>56.5</v>
       </c>
       <c r="U16">
-        <v>1.64</v>
+        <v>41.75</v>
       </c>
       <c r="V16">
-        <v>-13.14</v>
+        <v>27.28</v>
       </c>
       <c r="W16">
-        <v>-26.91</v>
+        <v>13.06</v>
       </c>
       <c r="X16">
-        <v>-39.96</v>
+        <v>-0.8</v>
       </c>
       <c r="Y16">
-        <v>-52.51</v>
+        <v>-14.17</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -10566,37 +10566,37 @@
         <v>165</v>
       </c>
       <c r="O17">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P17">
-        <v>86.47</v>
+        <v>118.85</v>
       </c>
       <c r="Q17">
-        <v>64.180000000000007</v>
+        <v>102.04</v>
       </c>
       <c r="R17">
-        <v>45.07</v>
+        <v>85.57</v>
       </c>
       <c r="S17">
-        <v>28.92</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="T17">
-        <v>13.92</v>
+        <v>54.05</v>
       </c>
       <c r="U17">
-        <v>-2.09</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="V17">
-        <v>-17.27</v>
+        <v>23.85</v>
       </c>
       <c r="W17">
-        <v>-31.44</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="X17">
-        <v>-44.85</v>
+        <v>-5.58</v>
       </c>
       <c r="Y17">
-        <v>-57.75</v>
+        <v>-19.86</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -10640,37 +10640,37 @@
         <v>170</v>
       </c>
       <c r="O18">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P18">
-        <v>85.52</v>
+        <v>118.52</v>
       </c>
       <c r="Q18">
-        <v>62.79</v>
+        <v>101.38</v>
       </c>
       <c r="R18">
-        <v>43.31</v>
+        <v>84.52</v>
       </c>
       <c r="S18">
-        <v>26.85</v>
+        <v>68.2</v>
       </c>
       <c r="T18">
-        <v>11.55</v>
+        <v>52.34</v>
       </c>
       <c r="U18">
-        <v>-4.7699999999999996</v>
+        <v>36.76</v>
       </c>
       <c r="V18">
-        <v>-20.25</v>
+        <v>21.37</v>
       </c>
       <c r="W18">
-        <v>-34.69</v>
+        <v>6.14</v>
       </c>
       <c r="X18">
-        <v>-48.36</v>
+        <v>-8.93</v>
       </c>
       <c r="Y18">
-        <v>-61.52</v>
+        <v>-23.78</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -10714,37 +10714,37 @@
         <v>175</v>
       </c>
       <c r="O19">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P19">
-        <v>84.95</v>
+        <v>118.32</v>
       </c>
       <c r="Q19">
-        <v>61.96</v>
+        <v>100.98</v>
       </c>
       <c r="R19">
-        <v>42.25</v>
+        <v>83.89</v>
       </c>
       <c r="S19">
-        <v>25.6</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="T19">
-        <v>10.119999999999999</v>
+        <v>51.32</v>
       </c>
       <c r="U19">
-        <v>-6.38</v>
+        <v>35.49</v>
       </c>
       <c r="V19">
-        <v>-22.05</v>
+        <v>19.84</v>
       </c>
       <c r="W19">
-        <v>-36.65</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="X19">
-        <v>-50.48</v>
+        <v>-11</v>
       </c>
       <c r="Y19">
-        <v>-63.79</v>
+        <v>-26.12</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -10788,37 +10788,37 @@
         <v>180</v>
       </c>
       <c r="O20">
-        <v>135.05000000000001</v>
+        <v>135.72</v>
       </c>
       <c r="P20">
-        <v>84.76</v>
+        <v>118.25</v>
       </c>
       <c r="Q20">
-        <v>61.68</v>
+        <v>100.85</v>
       </c>
       <c r="R20">
-        <v>41.89</v>
+        <v>83.67</v>
       </c>
       <c r="S20">
-        <v>25.18</v>
+        <v>67.14</v>
       </c>
       <c r="T20">
-        <v>9.65</v>
+        <v>50.99</v>
       </c>
       <c r="U20">
-        <v>-6.92</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="V20">
-        <v>-22.65</v>
+        <v>19.29</v>
       </c>
       <c r="W20">
-        <v>-37.31</v>
+        <v>3.71</v>
       </c>
       <c r="X20">
-        <v>-51.19</v>
+        <v>-11.71</v>
       </c>
       <c r="Y20">
-        <v>-64.55</v>
+        <v>-26.92</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -11705,37 +11705,37 @@
         <v>90</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P2">
-        <v>51.6</v>
+        <v>44.53</v>
       </c>
       <c r="Q2">
-        <v>86.27</v>
+        <v>88.52</v>
       </c>
       <c r="R2">
-        <v>116.55</v>
+        <v>127.42</v>
       </c>
       <c r="S2">
-        <v>144.27000000000001</v>
+        <v>156.63999999999999</v>
       </c>
       <c r="T2">
-        <v>168.9</v>
+        <v>178.99</v>
       </c>
       <c r="U2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="V2">
-        <v>207.22</v>
+        <v>211.64</v>
       </c>
       <c r="W2">
-        <v>222.05</v>
+        <v>224.47</v>
       </c>
       <c r="X2">
-        <v>235.76</v>
+        <v>236</v>
       </c>
       <c r="Y2">
-        <v>248.75</v>
+        <v>246.71</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -11779,37 +11779,37 @@
         <v>95</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P3">
-        <v>51.4</v>
+        <v>44.37</v>
       </c>
       <c r="Q3">
-        <v>85.94</v>
+        <v>88.2</v>
       </c>
       <c r="R3">
-        <v>116.1</v>
+        <v>127.44</v>
       </c>
       <c r="S3">
-        <v>143.72</v>
+        <v>157.1</v>
       </c>
       <c r="T3">
-        <v>168.25</v>
+        <v>179.74</v>
       </c>
       <c r="U3">
-        <v>189.28</v>
+        <v>197.65</v>
       </c>
       <c r="V3">
-        <v>206.43</v>
+        <v>212.34</v>
       </c>
       <c r="W3">
-        <v>221.21</v>
+        <v>225.31</v>
       </c>
       <c r="X3">
-        <v>234.87</v>
+        <v>237.01</v>
       </c>
       <c r="Y3">
-        <v>247.81</v>
+        <v>247.87</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -11853,37 +11853,37 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P4">
-        <v>50.81</v>
+        <v>43.87</v>
       </c>
       <c r="Q4">
-        <v>84.96</v>
+        <v>87.2</v>
       </c>
       <c r="R4">
-        <v>114.78</v>
+        <v>126.53</v>
       </c>
       <c r="S4">
-        <v>142.07</v>
+        <v>156.63999999999999</v>
       </c>
       <c r="T4">
-        <v>166.33</v>
+        <v>179.55</v>
       </c>
       <c r="U4">
-        <v>187.11</v>
+        <v>197.39</v>
       </c>
       <c r="V4">
-        <v>204.07</v>
+        <v>212.13</v>
       </c>
       <c r="W4">
-        <v>218.68</v>
+        <v>225.27</v>
       </c>
       <c r="X4">
-        <v>232.18</v>
+        <v>237.12</v>
       </c>
       <c r="Y4">
-        <v>244.97</v>
+        <v>248.12</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -11927,37 +11927,37 @@
         <v>105</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P5">
-        <v>49.84</v>
+        <v>43.03</v>
       </c>
       <c r="Q5">
-        <v>83.33</v>
+        <v>85.55</v>
       </c>
       <c r="R5">
-        <v>112.58</v>
+        <v>124.64</v>
       </c>
       <c r="S5">
-        <v>139.35</v>
+        <v>155.24</v>
       </c>
       <c r="T5">
-        <v>163.13999999999999</v>
+        <v>178.39</v>
       </c>
       <c r="U5">
-        <v>183.53</v>
+        <v>196.2</v>
       </c>
       <c r="V5">
-        <v>200.16</v>
+        <v>210.96</v>
       </c>
       <c r="W5">
-        <v>214.49</v>
+        <v>224.23</v>
       </c>
       <c r="X5">
-        <v>227.73</v>
+        <v>236.28</v>
       </c>
       <c r="Y5">
-        <v>240.28</v>
+        <v>247.4</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -12001,37 +12001,37 @@
         <v>110</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P6">
-        <v>48.48</v>
+        <v>41.86</v>
       </c>
       <c r="Q6">
-        <v>81.069999999999993</v>
+        <v>83.25</v>
       </c>
       <c r="R6">
-        <v>109.52</v>
+        <v>121.71</v>
       </c>
       <c r="S6">
-        <v>135.57</v>
+        <v>152.81</v>
       </c>
       <c r="T6">
-        <v>158.71</v>
+        <v>176.26</v>
       </c>
       <c r="U6">
-        <v>178.54</v>
+        <v>194.09</v>
       </c>
       <c r="V6">
-        <v>194.72</v>
+        <v>208.84</v>
       </c>
       <c r="W6">
-        <v>208.66</v>
+        <v>222.16</v>
       </c>
       <c r="X6">
-        <v>221.55</v>
+        <v>234.4</v>
       </c>
       <c r="Y6">
-        <v>233.75</v>
+        <v>245.65</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -12075,37 +12075,37 @@
         <v>115</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P7">
-        <v>46.76</v>
+        <v>40.369999999999997</v>
       </c>
       <c r="Q7">
-        <v>78.19</v>
+        <v>80.319999999999993</v>
       </c>
       <c r="R7">
-        <v>105.63</v>
+        <v>117.72</v>
       </c>
       <c r="S7">
-        <v>130.75</v>
+        <v>149.25</v>
       </c>
       <c r="T7">
-        <v>153.07</v>
+        <v>173.09</v>
       </c>
       <c r="U7">
-        <v>172.2</v>
+        <v>191.05</v>
       </c>
       <c r="V7">
-        <v>187.8</v>
+        <v>205.76</v>
       </c>
       <c r="W7">
-        <v>201.25</v>
+        <v>219.03</v>
       </c>
       <c r="X7">
-        <v>213.68</v>
+        <v>231.37</v>
       </c>
       <c r="Y7">
-        <v>225.45</v>
+        <v>242.78</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -12149,37 +12149,37 @@
         <v>120</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P8">
-        <v>44.68</v>
+        <v>38.57</v>
       </c>
       <c r="Q8">
-        <v>74.709999999999994</v>
+        <v>76.78</v>
       </c>
       <c r="R8">
-        <v>100.93</v>
+        <v>112.74</v>
       </c>
       <c r="S8">
-        <v>124.94</v>
+        <v>144.36000000000001</v>
       </c>
       <c r="T8">
-        <v>146.27000000000001</v>
+        <v>168.73</v>
       </c>
       <c r="U8">
-        <v>164.55</v>
+        <v>187</v>
       </c>
       <c r="V8">
-        <v>179.46</v>
+        <v>201.67</v>
       </c>
       <c r="W8">
-        <v>192.3</v>
+        <v>214.83</v>
       </c>
       <c r="X8">
-        <v>204.18</v>
+        <v>227.1</v>
       </c>
       <c r="Y8">
-        <v>215.43</v>
+        <v>238.63</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -12223,37 +12223,37 @@
         <v>125</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P9">
-        <v>42.26</v>
+        <v>36.47</v>
       </c>
       <c r="Q9">
-        <v>70.67</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="R9">
-        <v>95.47</v>
+        <v>106.84</v>
       </c>
       <c r="S9">
-        <v>118.18</v>
+        <v>137.88</v>
       </c>
       <c r="T9">
-        <v>138.35</v>
+        <v>162.91999999999999</v>
       </c>
       <c r="U9">
-        <v>155.63999999999999</v>
+        <v>181.75</v>
       </c>
       <c r="V9">
-        <v>169.74</v>
+        <v>196.48</v>
       </c>
       <c r="W9">
-        <v>181.9</v>
+        <v>209.48</v>
       </c>
       <c r="X9">
-        <v>193.13</v>
+        <v>221.58</v>
       </c>
       <c r="Y9">
-        <v>203.77</v>
+        <v>233.01</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -12297,37 +12297,37 @@
         <v>130</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P10">
-        <v>39.520000000000003</v>
+        <v>34.090000000000003</v>
       </c>
       <c r="Q10">
-        <v>66.09</v>
+        <v>67.97</v>
       </c>
       <c r="R10">
-        <v>89.28</v>
+        <v>100.09</v>
       </c>
       <c r="S10">
-        <v>110.52</v>
+        <v>129.84</v>
       </c>
       <c r="T10">
-        <v>129.38999999999999</v>
+        <v>155.26</v>
       </c>
       <c r="U10">
-        <v>145.55000000000001</v>
+        <v>174.95</v>
       </c>
       <c r="V10">
-        <v>158.74</v>
+        <v>189.94</v>
       </c>
       <c r="W10">
-        <v>170.1</v>
+        <v>202.85</v>
       </c>
       <c r="X10">
-        <v>180.61</v>
+        <v>214.69</v>
       </c>
       <c r="Y10">
-        <v>190.56</v>
+        <v>225.89</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -12371,37 +12371,37 @@
         <v>135</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P11">
-        <v>36.479999999999997</v>
+        <v>31.45</v>
       </c>
       <c r="Q11">
-        <v>61</v>
+        <v>62.77</v>
       </c>
       <c r="R11">
-        <v>82.41</v>
+        <v>92.56</v>
       </c>
       <c r="S11">
-        <v>102.01</v>
+        <v>120.46</v>
       </c>
       <c r="T11">
-        <v>119.43</v>
+        <v>145.41999999999999</v>
       </c>
       <c r="U11">
-        <v>134.35</v>
+        <v>165.89</v>
       </c>
       <c r="V11">
-        <v>146.53</v>
+        <v>181.52</v>
       </c>
       <c r="W11">
-        <v>157.02000000000001</v>
+        <v>194.54</v>
       </c>
       <c r="X11">
-        <v>166.71</v>
+        <v>206.22</v>
       </c>
       <c r="Y11">
-        <v>175.9</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -12445,37 +12445,37 @@
         <v>140</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P12">
-        <v>33.17</v>
+        <v>28.57</v>
       </c>
       <c r="Q12">
-        <v>55.46</v>
+        <v>57.08</v>
       </c>
       <c r="R12">
-        <v>74.92</v>
+        <v>84.29</v>
       </c>
       <c r="S12">
-        <v>92.74</v>
+        <v>109.94</v>
       </c>
       <c r="T12">
-        <v>108.57</v>
+        <v>133.63999999999999</v>
       </c>
       <c r="U12">
-        <v>122.13</v>
+        <v>154.05000000000001</v>
       </c>
       <c r="V12">
-        <v>133.19999999999999</v>
+        <v>170.3</v>
       </c>
       <c r="W12">
-        <v>142.72999999999999</v>
+        <v>183.74</v>
       </c>
       <c r="X12">
-        <v>151.55000000000001</v>
+        <v>195.52</v>
       </c>
       <c r="Y12">
-        <v>159.9</v>
+        <v>206.28</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -12519,37 +12519,37 @@
         <v>145</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P13">
-        <v>29.59</v>
+        <v>25.47</v>
       </c>
       <c r="Q13">
-        <v>49.48</v>
+        <v>50.95</v>
       </c>
       <c r="R13">
-        <v>66.849999999999994</v>
+        <v>75.34</v>
       </c>
       <c r="S13">
-        <v>82.75</v>
+        <v>98.42</v>
       </c>
       <c r="T13">
-        <v>96.88</v>
+        <v>120.19</v>
       </c>
       <c r="U13">
-        <v>108.98</v>
+        <v>139.88</v>
       </c>
       <c r="V13">
-        <v>118.86</v>
+        <v>156.22999999999999</v>
       </c>
       <c r="W13">
-        <v>127.37</v>
+        <v>169.45</v>
       </c>
       <c r="X13">
-        <v>135.22999999999999</v>
+        <v>181.15</v>
       </c>
       <c r="Y13">
-        <v>142.68</v>
+        <v>191.94</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -12593,37 +12593,37 @@
         <v>150</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P14">
-        <v>25.8</v>
+        <v>22.19</v>
       </c>
       <c r="Q14">
-        <v>43.14</v>
+        <v>44.42</v>
       </c>
       <c r="R14">
-        <v>58.28</v>
+        <v>65.78</v>
       </c>
       <c r="S14">
-        <v>72.14</v>
+        <v>86.04</v>
       </c>
       <c r="T14">
-        <v>84.45</v>
+        <v>105.36</v>
       </c>
       <c r="U14">
-        <v>95</v>
+        <v>123.45</v>
       </c>
       <c r="V14">
-        <v>103.61</v>
+        <v>139.56</v>
       </c>
       <c r="W14">
-        <v>111.03</v>
+        <v>152.61000000000001</v>
       </c>
       <c r="X14">
-        <v>117.88</v>
+        <v>163.58000000000001</v>
       </c>
       <c r="Y14">
-        <v>124.38</v>
+        <v>173.47</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -12667,37 +12667,37 @@
         <v>155</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P15">
-        <v>21.81</v>
+        <v>18.739999999999998</v>
       </c>
       <c r="Q15">
-        <v>36.46</v>
+        <v>37.54</v>
       </c>
       <c r="R15">
-        <v>49.26</v>
+        <v>55.67</v>
       </c>
       <c r="S15">
-        <v>60.97</v>
+        <v>72.91</v>
       </c>
       <c r="T15">
-        <v>71.38</v>
+        <v>89.42</v>
       </c>
       <c r="U15">
-        <v>80.3</v>
+        <v>105.19</v>
       </c>
       <c r="V15">
-        <v>87.58</v>
+        <v>119.94</v>
       </c>
       <c r="W15">
-        <v>93.85</v>
+        <v>133.03</v>
       </c>
       <c r="X15">
-        <v>99.64</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="Y15">
-        <v>105.13</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -12741,37 +12741,37 @@
         <v>160</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P16">
-        <v>17.649999999999999</v>
+        <v>15.16</v>
       </c>
       <c r="Q16">
-        <v>29.51</v>
+        <v>30.37</v>
       </c>
       <c r="R16">
-        <v>39.86</v>
+        <v>45.11</v>
       </c>
       <c r="S16">
-        <v>49.35</v>
+        <v>59.15</v>
       </c>
       <c r="T16">
-        <v>57.77</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="U16">
-        <v>64.989999999999995</v>
+        <v>85.66</v>
       </c>
       <c r="V16">
-        <v>70.87</v>
+        <v>98.24</v>
       </c>
       <c r="W16">
-        <v>75.95</v>
+        <v>110.04</v>
       </c>
       <c r="X16">
-        <v>80.64</v>
+        <v>120.54</v>
       </c>
       <c r="Y16">
-        <v>85.08</v>
+        <v>129.41</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -12815,37 +12815,37 @@
         <v>165</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P17">
-        <v>13.35</v>
+        <v>11.46</v>
       </c>
       <c r="Q17">
-        <v>22.33</v>
+        <v>22.97</v>
       </c>
       <c r="R17">
-        <v>30.17</v>
+        <v>34.17</v>
       </c>
       <c r="S17">
-        <v>37.340000000000003</v>
+        <v>44.87</v>
       </c>
       <c r="T17">
-        <v>43.72</v>
+        <v>55.2</v>
       </c>
       <c r="U17">
-        <v>49.18</v>
+        <v>65.25</v>
       </c>
       <c r="V17">
-        <v>53.63</v>
+        <v>75.010000000000005</v>
       </c>
       <c r="W17">
-        <v>57.47</v>
+        <v>84.43</v>
       </c>
       <c r="X17">
-        <v>61.02</v>
+        <v>93.35</v>
       </c>
       <c r="Y17">
-        <v>64.38</v>
+        <v>101.42</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -12889,37 +12889,37 @@
         <v>170</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P18">
-        <v>8.9600000000000009</v>
+        <v>7.68</v>
       </c>
       <c r="Q18">
-        <v>14.98</v>
+        <v>15.39</v>
       </c>
       <c r="R18">
-        <v>20.239999999999998</v>
+        <v>22.95</v>
       </c>
       <c r="S18">
-        <v>25.06</v>
+        <v>30.19</v>
       </c>
       <c r="T18">
-        <v>29.33</v>
+        <v>37.31</v>
       </c>
       <c r="U18">
-        <v>33</v>
+        <v>44.15</v>
       </c>
       <c r="V18">
-        <v>35.99</v>
+        <v>50.78</v>
       </c>
       <c r="W18">
-        <v>38.56</v>
+        <v>57.21</v>
       </c>
       <c r="X18">
-        <v>40.94</v>
+        <v>63.44</v>
       </c>
       <c r="Y18">
-        <v>43.2</v>
+        <v>69.41</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -12963,37 +12963,37 @@
         <v>175</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q19">
-        <v>7.52</v>
+        <v>7.71</v>
       </c>
       <c r="R19">
-        <v>10.16</v>
+        <v>11.51</v>
       </c>
       <c r="S19">
-        <v>12.58</v>
+        <v>15.2</v>
       </c>
       <c r="T19">
-        <v>14.72</v>
+        <v>18.88</v>
       </c>
       <c r="U19">
-        <v>16.559999999999999</v>
+        <v>22.41</v>
       </c>
       <c r="V19">
-        <v>18.059999999999999</v>
+        <v>25.76</v>
       </c>
       <c r="W19">
-        <v>19.36</v>
+        <v>28.98</v>
       </c>
       <c r="X19">
-        <v>20.55</v>
+        <v>32.090000000000003</v>
       </c>
       <c r="Y19">
-        <v>21.68</v>
+        <v>35.119999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -13037,37 +13037,37 @@
         <v>180</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">

--- a/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
+++ b/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
@@ -1232,61 +1232,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>135.66999999999999</c:v>
+                  <c:v>135.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134.16</c:v>
+                  <c:v>131.24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132.65</c:v>
+                  <c:v>126.79</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>131.16999999999999</c:v>
+                  <c:v>122.39</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>129.72</c:v>
+                  <c:v>118.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>128.32</c:v>
+                  <c:v>113.86</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>126.97</c:v>
+                  <c:v>109.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>125.69</c:v>
+                  <c:v>105.97</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>124.48</c:v>
+                  <c:v>102.34</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>123.36</c:v>
+                  <c:v>98.96</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>122.33</c:v>
+                  <c:v>96.33</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>121.41</c:v>
+                  <c:v>94.35</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>120.59</c:v>
+                  <c:v>92.59</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>119.89</c:v>
+                  <c:v>91.06</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>119.31</c:v>
+                  <c:v>89.79</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>118.85</c:v>
+                  <c:v>88.79</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>118.52</c:v>
+                  <c:v>88.1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>118.32</c:v>
+                  <c:v>87.68</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>118.25</c:v>
+                  <c:v>87.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1315,61 +1315,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>119.74</c:v>
+                  <c:v>135.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>109.84</c:v>
+                  <c:v>103.64</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99.45</c:v>
+                  <c:v>84.74</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>88.64</c:v>
+                  <c:v>69.94</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.849999999999994</c:v>
+                  <c:v>56.34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.31</c:v>
+                  <c:v>43.64</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>57.07</c:v>
+                  <c:v>30.9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>47.15</c:v>
+                  <c:v>18.72</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>37.58</c:v>
+                  <c:v>8.15</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>28.34</c:v>
+                  <c:v>-2.25</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>19.399999999999999</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>10.32</c:v>
+                  <c:v>-28.43</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.05</c:v>
+                  <c:v>-46.13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-7.16</c:v>
+                  <c:v>-62.92</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-14.17</c:v>
+                  <c:v>-75.64</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-19.86</c:v>
+                  <c:v>-81.87</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-23.78</c:v>
+                  <c:v>-86</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-26.12</c:v>
+                  <c:v>-88.19</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-26.92</c:v>
+                  <c:v>-88.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1385,11 +1385,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-580418848"/>
-        <c:axId val="-580425920"/>
+        <c:axId val="-195327808"/>
+        <c:axId val="-195340864"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-580418848"/>
+        <c:axId val="-195327808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1432,7 +1432,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580425920"/>
+        <c:crossAx val="-195340864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1440,7 +1440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-580425920"/>
+        <c:axId val="-195340864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1491,7 +1491,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580418848"/>
+        <c:crossAx val="-195327808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1894,34 +1894,34 @@
                   <c:v>135.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134.16</c:v>
+                  <c:v>131.24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132.65</c:v>
+                  <c:v>128.36000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>130.69999999999999</c:v>
+                  <c:v>124.68</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>127.54</c:v>
+                  <c:v>121.73</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>123.92</c:v>
+                  <c:v>118.23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>120.71</c:v>
+                  <c:v>114.73</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>117.96</c:v>
+                  <c:v>111.66</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>115.28</c:v>
+                  <c:v>108.38</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>112.58</c:v>
+                  <c:v>105.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>109.84</c:v>
+                  <c:v>103.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2230,34 +2230,34 @@
                   <c:v>135.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118.25</c:v>
+                  <c:v>87.54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100.85</c:v>
+                  <c:v>54.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83.67</c:v>
+                  <c:v>25.64</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.14</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.99</c:v>
+                  <c:v>-11.65</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.049999999999997</c:v>
+                  <c:v>-29.83</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.29</c:v>
+                  <c:v>-44.56</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.71</c:v>
+                  <c:v>-59.29</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-11.71</c:v>
+                  <c:v>-74.02</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-26.92</c:v>
+                  <c:v>-88.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,11 +2273,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-580431360"/>
-        <c:axId val="-580419392"/>
+        <c:axId val="-195332160"/>
+        <c:axId val="-195343040"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-580431360"/>
+        <c:axId val="-195332160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2320,7 +2320,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580419392"/>
+        <c:crossAx val="-195343040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2328,7 +2328,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-580419392"/>
+        <c:axId val="-195343040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2379,7 +2379,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580431360"/>
+        <c:crossAx val="-195332160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2982,34 +2982,34 @@
                   <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.53</c:v>
+                  <c:v>53.13</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.52</c:v>
+                  <c:v>105.68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>127.42</c:v>
+                  <c:v>156.88</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>156.63999999999999</c:v>
+                  <c:v>202.83</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>178.99</c:v>
+                  <c:v>245.33</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>197</c:v>
+                  <c:v>287.83999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>211.64</c:v>
+                  <c:v>325.43</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>224.47</c:v>
+                  <c:v>344.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>236</c:v>
+                  <c:v>363.08</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>246.71</c:v>
+                  <c:v>381.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3094,34 +3094,34 @@
                   <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.85</c:v>
+                  <c:v>4.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.71</c:v>
+                  <c:v>9.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.51</c:v>
+                  <c:v>13.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.2</c:v>
+                  <c:v>17.829999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18.88</c:v>
+                  <c:v>22.29</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>22.41</c:v>
+                  <c:v>24.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.76</c:v>
+                  <c:v>25.91</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28.98</c:v>
+                  <c:v>29.62</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>32.090000000000003</c:v>
+                  <c:v>33.32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35.119999999999997</c:v>
+                  <c:v>37.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3137,11 +3137,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-580429728"/>
-        <c:axId val="-580423744"/>
+        <c:axId val="-195342496"/>
+        <c:axId val="-195340320"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-580429728"/>
+        <c:axId val="-195342496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3184,7 +3184,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580423744"/>
+        <c:crossAx val="-195340320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3192,7 +3192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-580423744"/>
+        <c:axId val="-195340320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3243,7 +3243,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580429728"/>
+        <c:crossAx val="-195342496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,61 +3763,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>246.71</c:v>
+                  <c:v>381.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>247.87</c:v>
+                  <c:v>381.19</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>248.12</c:v>
+                  <c:v>379.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>247.4</c:v>
+                  <c:v>375.49</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>245.65</c:v>
+                  <c:v>370.55</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>242.78</c:v>
+                  <c:v>362.26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>238.63</c:v>
+                  <c:v>344.61</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>233.01</c:v>
+                  <c:v>325.20999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>225.89</c:v>
+                  <c:v>304.19</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>217.1</c:v>
+                  <c:v>279.95</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>206.28</c:v>
+                  <c:v>251.92</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>191.94</c:v>
+                  <c:v>222.06</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>173.47</c:v>
+                  <c:v>190.94</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>153</c:v>
+                  <c:v>159.11000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>129.41</c:v>
+                  <c:v>127.1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>101.42</c:v>
+                  <c:v>95.52</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69.41</c:v>
+                  <c:v>66.34</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>35.119999999999997</c:v>
+                  <c:v>37.03</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.03</c:v>
+                  <c:v>-0.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4243,58 +4243,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>44.53</c:v>
+                  <c:v>53.13</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.37</c:v>
+                  <c:v>52.92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.87</c:v>
+                  <c:v>52.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.03</c:v>
+                  <c:v>51.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41.86</c:v>
+                  <c:v>49.92</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.369999999999997</c:v>
+                  <c:v>48.15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38.57</c:v>
+                  <c:v>46.01</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.47</c:v>
+                  <c:v>43.52</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>34.090000000000003</c:v>
+                  <c:v>40.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>31.45</c:v>
+                  <c:v>37.56</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>28.57</c:v>
+                  <c:v>34.15</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25.47</c:v>
+                  <c:v>30.47</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>22.19</c:v>
+                  <c:v>26.56</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.739999999999998</c:v>
+                  <c:v>22.45</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15.16</c:v>
+                  <c:v>18.16</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11.46</c:v>
+                  <c:v>13.74</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.68</c:v>
+                  <c:v>9.2200000000000006</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.85</c:v>
+                  <c:v>4.62</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.01</c:v>
@@ -4313,11 +4313,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-580418304"/>
-        <c:axId val="-580427552"/>
+        <c:axId val="-195335968"/>
+        <c:axId val="-195332704"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-580418304"/>
+        <c:axId val="-195335968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4360,7 +4360,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580427552"/>
+        <c:crossAx val="-195332704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4368,7 +4368,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-580427552"/>
+        <c:axId val="-195332704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4419,7 +4419,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580418304"/>
+        <c:crossAx val="-195335968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4515,7 +4515,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4925,11 +4924,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-580416672"/>
-        <c:axId val="-580429184"/>
+        <c:axId val="-195341952"/>
+        <c:axId val="-195339232"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-580416672"/>
+        <c:axId val="-195341952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4971,7 +4970,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580429184"/>
+        <c:crossAx val="-195339232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4979,7 +4978,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-580429184"/>
+        <c:axId val="-195339232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5030,7 +5029,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580416672"/>
+        <c:crossAx val="-195341952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5388,11 +5387,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-580428640"/>
-        <c:axId val="-580427008"/>
+        <c:axId val="-195329984"/>
+        <c:axId val="-195335424"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-580428640"/>
+        <c:axId val="-195329984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5434,7 +5433,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580427008"/>
+        <c:crossAx val="-195335424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5442,7 +5441,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-580427008"/>
+        <c:axId val="-195335424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5493,7 +5492,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-580428640"/>
+        <c:crossAx val="-195329984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9459,34 +9458,34 @@
         <v>135.72</v>
       </c>
       <c r="P2">
-        <v>135.66999999999999</v>
+        <v>135.72</v>
       </c>
       <c r="Q2">
-        <v>135.6</v>
+        <v>135.72999999999999</v>
       </c>
       <c r="R2">
-        <v>134.72</v>
+        <v>135.74</v>
       </c>
       <c r="S2">
-        <v>132.47999999999999</v>
+        <v>135.74</v>
       </c>
       <c r="T2">
-        <v>129.72999999999999</v>
+        <v>135.74</v>
       </c>
       <c r="U2">
-        <v>127.23</v>
+        <v>135.74</v>
       </c>
       <c r="V2">
-        <v>125.26</v>
+        <v>135.74</v>
       </c>
       <c r="W2">
-        <v>123.41</v>
+        <v>135.74</v>
       </c>
       <c r="X2">
-        <v>121.57</v>
+        <v>135.74</v>
       </c>
       <c r="Y2">
-        <v>119.74</v>
+        <v>135.74</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -9533,34 +9532,34 @@
         <v>135.72</v>
       </c>
       <c r="P3">
-        <v>134.16</v>
+        <v>131.24</v>
       </c>
       <c r="Q3">
-        <v>132.65</v>
+        <v>128.36000000000001</v>
       </c>
       <c r="R3">
-        <v>130.69999999999999</v>
+        <v>124.68</v>
       </c>
       <c r="S3">
-        <v>127.54</v>
+        <v>121.73</v>
       </c>
       <c r="T3">
-        <v>123.92</v>
+        <v>118.23</v>
       </c>
       <c r="U3">
-        <v>120.71</v>
+        <v>114.73</v>
       </c>
       <c r="V3">
-        <v>117.96</v>
+        <v>111.66</v>
       </c>
       <c r="W3">
-        <v>115.28</v>
+        <v>108.38</v>
       </c>
       <c r="X3">
-        <v>112.58</v>
+        <v>105.72</v>
       </c>
       <c r="Y3">
-        <v>109.84</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -9607,34 +9606,34 @@
         <v>135.72</v>
       </c>
       <c r="P4">
-        <v>132.65</v>
+        <v>126.79</v>
       </c>
       <c r="Q4">
-        <v>129.69999999999999</v>
+        <v>121.04</v>
       </c>
       <c r="R4">
-        <v>126.66</v>
+        <v>113.7</v>
       </c>
       <c r="S4">
-        <v>122.56</v>
+        <v>107.83</v>
       </c>
       <c r="T4">
-        <v>118.04</v>
+        <v>102.91</v>
       </c>
       <c r="U4">
-        <v>114.03</v>
+        <v>98.61</v>
       </c>
       <c r="V4">
-        <v>110.44</v>
+        <v>94.96</v>
       </c>
       <c r="W4">
-        <v>106.87</v>
+        <v>91.3</v>
       </c>
       <c r="X4">
-        <v>103.2</v>
+        <v>87.76</v>
       </c>
       <c r="Y4">
-        <v>99.45</v>
+        <v>84.74</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -9681,34 +9680,34 @@
         <v>135.72</v>
       </c>
       <c r="P5">
-        <v>131.16999999999999</v>
+        <v>122.39</v>
       </c>
       <c r="Q5">
-        <v>126.78</v>
+        <v>113.32</v>
       </c>
       <c r="R5">
-        <v>122.6</v>
+        <v>103.52</v>
       </c>
       <c r="S5">
-        <v>117.56</v>
+        <v>98.53</v>
       </c>
       <c r="T5">
-        <v>112.08</v>
+        <v>92.36</v>
       </c>
       <c r="U5">
-        <v>107.15</v>
+        <v>86.48</v>
       </c>
       <c r="V5">
-        <v>102.61</v>
+        <v>82.56</v>
       </c>
       <c r="W5">
-        <v>98.08</v>
+        <v>78.73</v>
       </c>
       <c r="X5">
-        <v>93.42</v>
+        <v>74.44</v>
       </c>
       <c r="Y5">
-        <v>88.64</v>
+        <v>69.94</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -9755,34 +9754,34 @@
         <v>135.72</v>
       </c>
       <c r="P6">
-        <v>129.72</v>
+        <v>118.06</v>
       </c>
       <c r="Q6">
-        <v>123.91</v>
+        <v>105.1</v>
       </c>
       <c r="R6">
-        <v>118.53</v>
+        <v>96.84</v>
       </c>
       <c r="S6">
-        <v>112.59</v>
+        <v>89.74</v>
       </c>
       <c r="T6">
-        <v>106.16</v>
+        <v>83.6</v>
       </c>
       <c r="U6">
-        <v>100.24</v>
+        <v>77.37</v>
       </c>
       <c r="V6">
-        <v>94.71</v>
+        <v>72.02</v>
       </c>
       <c r="W6">
-        <v>89.2</v>
+        <v>66.680000000000007</v>
       </c>
       <c r="X6">
-        <v>83.6</v>
+        <v>61.58</v>
       </c>
       <c r="Y6">
-        <v>77.849999999999994</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -9829,34 +9828,34 @@
         <v>135.72</v>
       </c>
       <c r="P7">
-        <v>128.32</v>
+        <v>113.86</v>
       </c>
       <c r="Q7">
-        <v>121.12</v>
+        <v>98.72</v>
       </c>
       <c r="R7">
-        <v>114.48</v>
+        <v>90.41</v>
       </c>
       <c r="S7">
-        <v>107.68</v>
+        <v>82.58</v>
       </c>
       <c r="T7">
-        <v>100.36</v>
+        <v>76.069999999999993</v>
       </c>
       <c r="U7">
-        <v>93.45</v>
+        <v>68.58</v>
       </c>
       <c r="V7">
-        <v>86.93</v>
+        <v>61.8</v>
       </c>
       <c r="W7">
-        <v>80.47</v>
+        <v>55.75</v>
       </c>
       <c r="X7">
-        <v>73.94</v>
+        <v>49.69</v>
       </c>
       <c r="Y7">
-        <v>67.31</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -9903,34 +9902,34 @@
         <v>135.72</v>
       </c>
       <c r="P8">
-        <v>126.97</v>
+        <v>109.82</v>
       </c>
       <c r="Q8">
-        <v>118.43</v>
+        <v>93.21</v>
       </c>
       <c r="R8">
-        <v>110.52</v>
+        <v>84.38</v>
       </c>
       <c r="S8">
-        <v>102.82</v>
+        <v>76.290000000000006</v>
       </c>
       <c r="T8">
-        <v>94.68</v>
+        <v>68.2</v>
       </c>
       <c r="U8">
-        <v>86.84</v>
+        <v>60.2</v>
       </c>
       <c r="V8">
-        <v>79.37</v>
+        <v>52.88</v>
       </c>
       <c r="W8">
-        <v>71.97</v>
+        <v>45.55</v>
       </c>
       <c r="X8">
-        <v>64.540000000000006</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="Y8">
-        <v>57.07</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -9977,34 +9976,34 @@
         <v>135.72</v>
       </c>
       <c r="P9">
-        <v>125.69</v>
+        <v>105.97</v>
       </c>
       <c r="Q9">
-        <v>115.86</v>
+        <v>87.85</v>
       </c>
       <c r="R9">
-        <v>106.7</v>
+        <v>77.989999999999995</v>
       </c>
       <c r="S9">
-        <v>97.97</v>
+        <v>70.239999999999995</v>
       </c>
       <c r="T9">
-        <v>89.12</v>
+        <v>60.64</v>
       </c>
       <c r="U9">
-        <v>80.41</v>
+        <v>52.02</v>
       </c>
       <c r="V9">
-        <v>72.05</v>
+        <v>44.35</v>
       </c>
       <c r="W9">
-        <v>63.76</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="X9">
-        <v>55.46</v>
+        <v>27.26</v>
       </c>
       <c r="Y9">
-        <v>47.15</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -10051,34 +10050,34 @@
         <v>135.72</v>
       </c>
       <c r="P10">
-        <v>124.48</v>
+        <v>102.34</v>
       </c>
       <c r="Q10">
-        <v>113.44</v>
+        <v>82.61</v>
       </c>
       <c r="R10">
-        <v>103.06</v>
+        <v>71.47</v>
       </c>
       <c r="S10">
-        <v>93.22</v>
+        <v>63.55</v>
       </c>
       <c r="T10">
-        <v>83.59</v>
+        <v>53.93</v>
       </c>
       <c r="U10">
-        <v>74.099999999999994</v>
+        <v>44.07</v>
       </c>
       <c r="V10">
-        <v>64.94</v>
+        <v>35.1</v>
       </c>
       <c r="W10">
-        <v>55.83</v>
+        <v>26.14</v>
       </c>
       <c r="X10">
-        <v>46.71</v>
+        <v>16.88</v>
       </c>
       <c r="Y10">
-        <v>37.58</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -10125,34 +10124,34 @@
         <v>135.72</v>
       </c>
       <c r="P11">
-        <v>123.36</v>
+        <v>98.96</v>
       </c>
       <c r="Q11">
-        <v>111.18</v>
+        <v>77.489999999999995</v>
       </c>
       <c r="R11">
-        <v>99.65</v>
+        <v>65.22</v>
       </c>
       <c r="S11">
-        <v>88.68</v>
+        <v>55.09</v>
       </c>
       <c r="T11">
-        <v>78.06</v>
+        <v>46.12</v>
       </c>
       <c r="U11">
-        <v>67.77</v>
+        <v>36.61</v>
       </c>
       <c r="V11">
-        <v>57.91</v>
+        <v>26.3</v>
       </c>
       <c r="W11">
-        <v>48.09</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="X11">
-        <v>38.22</v>
+        <v>6.71</v>
       </c>
       <c r="Y11">
-        <v>28.34</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -10199,34 +10198,34 @@
         <v>135.72</v>
       </c>
       <c r="P12">
-        <v>122.33</v>
+        <v>96.33</v>
       </c>
       <c r="Q12">
-        <v>109.1</v>
+        <v>73.02</v>
       </c>
       <c r="R12">
-        <v>96.5</v>
+        <v>59.1</v>
       </c>
       <c r="S12">
-        <v>84.44</v>
+        <v>47.13</v>
       </c>
       <c r="T12">
-        <v>72.75</v>
+        <v>36.47</v>
       </c>
       <c r="U12">
-        <v>61.44</v>
+        <v>25.77</v>
       </c>
       <c r="V12">
-        <v>50.73</v>
+        <v>15.72</v>
       </c>
       <c r="W12">
-        <v>40.340000000000003</v>
+        <v>6.34</v>
       </c>
       <c r="X12">
-        <v>29.9</v>
+        <v>-2.96</v>
       </c>
       <c r="Y12">
-        <v>19.399999999999999</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -10273,34 +10272,34 @@
         <v>135.72</v>
       </c>
       <c r="P13">
-        <v>121.41</v>
+        <v>94.35</v>
       </c>
       <c r="Q13">
-        <v>107.22</v>
+        <v>69.13</v>
       </c>
       <c r="R13">
-        <v>93.62</v>
+        <v>53.26</v>
       </c>
       <c r="S13">
-        <v>80.569999999999993</v>
+        <v>39.44</v>
       </c>
       <c r="T13">
-        <v>67.87</v>
+        <v>26.97</v>
       </c>
       <c r="U13">
-        <v>55.51</v>
+        <v>14.5</v>
       </c>
       <c r="V13">
-        <v>43.66</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="W13">
-        <v>32.380000000000003</v>
+        <v>-7.98</v>
       </c>
       <c r="X13">
-        <v>21.3</v>
+        <v>-18.190000000000001</v>
       </c>
       <c r="Y13">
-        <v>10.32</v>
+        <v>-28.43</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -10347,34 +10346,34 @@
         <v>135.72</v>
       </c>
       <c r="P14">
-        <v>120.59</v>
+        <v>92.59</v>
       </c>
       <c r="Q14">
-        <v>105.56</v>
+        <v>65.48</v>
       </c>
       <c r="R14">
-        <v>91.07</v>
+        <v>47.78</v>
       </c>
       <c r="S14">
-        <v>77.11</v>
+        <v>32.130000000000003</v>
       </c>
       <c r="T14">
-        <v>63.49</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="U14">
-        <v>50.18</v>
+        <v>3.53</v>
       </c>
       <c r="V14">
-        <v>37.25</v>
+        <v>-10.28</v>
       </c>
       <c r="W14">
-        <v>24.87</v>
+        <v>-22.23</v>
       </c>
       <c r="X14">
-        <v>12.85</v>
+        <v>-34.18</v>
       </c>
       <c r="Y14">
-        <v>1.05</v>
+        <v>-46.13</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -10421,34 +10420,34 @@
         <v>135.72</v>
       </c>
       <c r="P15">
-        <v>119.89</v>
+        <v>91.06</v>
       </c>
       <c r="Q15">
-        <v>104.14</v>
+        <v>62.09</v>
       </c>
       <c r="R15">
-        <v>88.86</v>
+        <v>42.7</v>
       </c>
       <c r="S15">
-        <v>74.099999999999994</v>
+        <v>25.26</v>
       </c>
       <c r="T15">
-        <v>59.69</v>
+        <v>9.24</v>
       </c>
       <c r="U15">
-        <v>45.55</v>
+        <v>-6.78</v>
       </c>
       <c r="V15">
-        <v>31.71</v>
+        <v>-21.98</v>
       </c>
       <c r="W15">
-        <v>18.309999999999999</v>
+        <v>-35.76</v>
       </c>
       <c r="X15">
-        <v>5.41</v>
+        <v>-49.36</v>
       </c>
       <c r="Y15">
-        <v>-7.16</v>
+        <v>-62.92</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -10495,34 +10494,34 @@
         <v>135.72</v>
       </c>
       <c r="P16">
-        <v>119.31</v>
+        <v>89.79</v>
       </c>
       <c r="Q16">
-        <v>102.96</v>
+        <v>59.01</v>
       </c>
       <c r="R16">
-        <v>87.02</v>
+        <v>38.07</v>
       </c>
       <c r="S16">
-        <v>71.58</v>
+        <v>18.87</v>
       </c>
       <c r="T16">
-        <v>56.5</v>
+        <v>1.36</v>
       </c>
       <c r="U16">
-        <v>41.75</v>
+        <v>-16.100000000000001</v>
       </c>
       <c r="V16">
-        <v>27.28</v>
+        <v>-32.33</v>
       </c>
       <c r="W16">
-        <v>13.06</v>
+        <v>-47.9</v>
       </c>
       <c r="X16">
-        <v>-0.8</v>
+        <v>-62.14</v>
       </c>
       <c r="Y16">
-        <v>-14.17</v>
+        <v>-75.64</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -10569,34 +10568,34 @@
         <v>135.72</v>
       </c>
       <c r="P17">
-        <v>118.85</v>
+        <v>88.79</v>
       </c>
       <c r="Q17">
-        <v>102.04</v>
+        <v>56.75</v>
       </c>
       <c r="R17">
-        <v>85.57</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="S17">
-        <v>69.599999999999994</v>
+        <v>13.51</v>
       </c>
       <c r="T17">
-        <v>54.05</v>
+        <v>-5.59</v>
       </c>
       <c r="U17">
-        <v>38.840000000000003</v>
+        <v>-23.7</v>
       </c>
       <c r="V17">
-        <v>23.85</v>
+        <v>-38.630000000000003</v>
       </c>
       <c r="W17">
-        <v>9.0299999999999994</v>
+        <v>-53.42</v>
       </c>
       <c r="X17">
-        <v>-5.58</v>
+        <v>-67.75</v>
       </c>
       <c r="Y17">
-        <v>-19.86</v>
+        <v>-81.87</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -10643,34 +10642,34 @@
         <v>135.72</v>
       </c>
       <c r="P18">
-        <v>118.52</v>
+        <v>88.1</v>
       </c>
       <c r="Q18">
-        <v>101.38</v>
+        <v>55.49</v>
       </c>
       <c r="R18">
-        <v>84.52</v>
+        <v>30.54</v>
       </c>
       <c r="S18">
-        <v>68.2</v>
+        <v>9.07</v>
       </c>
       <c r="T18">
-        <v>52.34</v>
+        <v>-9.64</v>
       </c>
       <c r="U18">
-        <v>36.76</v>
+        <v>-26.59</v>
       </c>
       <c r="V18">
-        <v>21.37</v>
+        <v>-41.82</v>
       </c>
       <c r="W18">
-        <v>6.14</v>
+        <v>-57.06</v>
       </c>
       <c r="X18">
-        <v>-8.93</v>
+        <v>-72</v>
       </c>
       <c r="Y18">
-        <v>-23.78</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -10717,34 +10716,34 @@
         <v>135.72</v>
       </c>
       <c r="P19">
-        <v>118.32</v>
+        <v>87.68</v>
       </c>
       <c r="Q19">
-        <v>100.98</v>
+        <v>54.77</v>
       </c>
       <c r="R19">
-        <v>83.89</v>
+        <v>27.7</v>
       </c>
       <c r="S19">
-        <v>67.400000000000006</v>
+        <v>7.28</v>
       </c>
       <c r="T19">
-        <v>51.32</v>
+        <v>-11.29</v>
       </c>
       <c r="U19">
-        <v>35.49</v>
+        <v>-28.63</v>
       </c>
       <c r="V19">
-        <v>19.84</v>
+        <v>-44.17</v>
       </c>
       <c r="W19">
-        <v>4.3499999999999996</v>
+        <v>-58.84</v>
       </c>
       <c r="X19">
-        <v>-11</v>
+        <v>-73.52</v>
       </c>
       <c r="Y19">
-        <v>-26.12</v>
+        <v>-88.19</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -10791,34 +10790,34 @@
         <v>135.72</v>
       </c>
       <c r="P20">
-        <v>118.25</v>
+        <v>87.54</v>
       </c>
       <c r="Q20">
-        <v>100.85</v>
+        <v>54.55</v>
       </c>
       <c r="R20">
-        <v>83.67</v>
+        <v>25.64</v>
       </c>
       <c r="S20">
-        <v>67.14</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>50.99</v>
+        <v>-11.65</v>
       </c>
       <c r="U20">
-        <v>35.049999999999997</v>
+        <v>-29.83</v>
       </c>
       <c r="V20">
-        <v>19.29</v>
+        <v>-44.56</v>
       </c>
       <c r="W20">
-        <v>3.71</v>
+        <v>-59.29</v>
       </c>
       <c r="X20">
-        <v>-11.71</v>
+        <v>-74.02</v>
       </c>
       <c r="Y20">
-        <v>-26.92</v>
+        <v>-88.75</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -11708,34 +11707,34 @@
         <v>-0.01</v>
       </c>
       <c r="P2">
-        <v>44.53</v>
+        <v>53.13</v>
       </c>
       <c r="Q2">
-        <v>88.52</v>
+        <v>105.68</v>
       </c>
       <c r="R2">
-        <v>127.42</v>
+        <v>156.88</v>
       </c>
       <c r="S2">
-        <v>156.63999999999999</v>
+        <v>202.83</v>
       </c>
       <c r="T2">
-        <v>178.99</v>
+        <v>245.33</v>
       </c>
       <c r="U2">
-        <v>197</v>
+        <v>287.83999999999997</v>
       </c>
       <c r="V2">
-        <v>211.64</v>
+        <v>325.43</v>
       </c>
       <c r="W2">
-        <v>224.47</v>
+        <v>344.25</v>
       </c>
       <c r="X2">
-        <v>236</v>
+        <v>363.08</v>
       </c>
       <c r="Y2">
-        <v>246.71</v>
+        <v>381.9</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -11782,34 +11781,34 @@
         <v>-0.01</v>
       </c>
       <c r="P3">
-        <v>44.37</v>
+        <v>52.92</v>
       </c>
       <c r="Q3">
-        <v>88.2</v>
+        <v>105.29</v>
       </c>
       <c r="R3">
-        <v>127.44</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="S3">
-        <v>157.1</v>
+        <v>202.18</v>
       </c>
       <c r="T3">
-        <v>179.74</v>
+        <v>244.53</v>
       </c>
       <c r="U3">
-        <v>197.65</v>
+        <v>286.87</v>
       </c>
       <c r="V3">
-        <v>212.34</v>
+        <v>322.89999999999998</v>
       </c>
       <c r="W3">
-        <v>225.31</v>
+        <v>343.68</v>
       </c>
       <c r="X3">
-        <v>237.01</v>
+        <v>362.43</v>
       </c>
       <c r="Y3">
-        <v>247.87</v>
+        <v>381.19</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -11856,34 +11855,34 @@
         <v>-0.01</v>
       </c>
       <c r="P4">
-        <v>43.87</v>
+        <v>52.32</v>
       </c>
       <c r="Q4">
-        <v>87.2</v>
+        <v>104.13</v>
       </c>
       <c r="R4">
-        <v>126.53</v>
+        <v>154.55000000000001</v>
       </c>
       <c r="S4">
-        <v>156.63999999999999</v>
+        <v>200.25</v>
       </c>
       <c r="T4">
-        <v>179.55</v>
+        <v>242.11</v>
       </c>
       <c r="U4">
-        <v>197.39</v>
+        <v>283.95999999999998</v>
       </c>
       <c r="V4">
-        <v>212.13</v>
+        <v>316.31</v>
       </c>
       <c r="W4">
-        <v>225.27</v>
+        <v>341.96</v>
       </c>
       <c r="X4">
-        <v>237.12</v>
+        <v>360.5</v>
       </c>
       <c r="Y4">
-        <v>248.12</v>
+        <v>379.04</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -11930,34 +11929,34 @@
         <v>-0.01</v>
       </c>
       <c r="P5">
-        <v>43.03</v>
+        <v>51.32</v>
       </c>
       <c r="Q5">
-        <v>85.55</v>
+        <v>102.13</v>
       </c>
       <c r="R5">
-        <v>124.64</v>
+        <v>151.65</v>
       </c>
       <c r="S5">
-        <v>155.24</v>
+        <v>196.47</v>
       </c>
       <c r="T5">
-        <v>178.39</v>
+        <v>238.09</v>
       </c>
       <c r="U5">
-        <v>196.2</v>
+        <v>279.14999999999998</v>
       </c>
       <c r="V5">
-        <v>210.96</v>
+        <v>308.18</v>
       </c>
       <c r="W5">
-        <v>224.23</v>
+        <v>336.04</v>
       </c>
       <c r="X5">
-        <v>236.28</v>
+        <v>357.3</v>
       </c>
       <c r="Y5">
-        <v>247.4</v>
+        <v>375.49</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -12004,34 +12003,34 @@
         <v>-0.01</v>
       </c>
       <c r="P6">
-        <v>41.86</v>
+        <v>49.92</v>
       </c>
       <c r="Q6">
-        <v>83.25</v>
+        <v>99.3</v>
       </c>
       <c r="R6">
-        <v>121.71</v>
+        <v>147.55000000000001</v>
       </c>
       <c r="S6">
-        <v>152.81</v>
+        <v>190.72</v>
       </c>
       <c r="T6">
-        <v>176.26</v>
+        <v>232.51</v>
       </c>
       <c r="U6">
-        <v>194.09</v>
+        <v>272.08999999999997</v>
       </c>
       <c r="V6">
-        <v>208.84</v>
+        <v>298.57</v>
       </c>
       <c r="W6">
-        <v>222.16</v>
+        <v>325.05</v>
       </c>
       <c r="X6">
-        <v>234.4</v>
+        <v>351.53</v>
       </c>
       <c r="Y6">
-        <v>245.65</v>
+        <v>370.55</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -12078,34 +12077,34 @@
         <v>-0.01</v>
       </c>
       <c r="P7">
-        <v>40.369999999999997</v>
+        <v>48.15</v>
       </c>
       <c r="Q7">
-        <v>80.319999999999993</v>
+        <v>95.73</v>
       </c>
       <c r="R7">
-        <v>117.72</v>
+        <v>142.25</v>
       </c>
       <c r="S7">
-        <v>149.25</v>
+        <v>183.65</v>
       </c>
       <c r="T7">
-        <v>173.09</v>
+        <v>225.05</v>
       </c>
       <c r="U7">
-        <v>191.05</v>
+        <v>262.64</v>
       </c>
       <c r="V7">
-        <v>205.76</v>
+        <v>287.55</v>
       </c>
       <c r="W7">
-        <v>219.03</v>
+        <v>312.45</v>
       </c>
       <c r="X7">
-        <v>231.37</v>
+        <v>337.35</v>
       </c>
       <c r="Y7">
-        <v>242.78</v>
+        <v>362.26</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -12152,34 +12151,34 @@
         <v>-0.01</v>
       </c>
       <c r="P8">
-        <v>38.57</v>
+        <v>46.01</v>
       </c>
       <c r="Q8">
-        <v>76.78</v>
+        <v>91.43</v>
       </c>
       <c r="R8">
-        <v>112.74</v>
+        <v>136</v>
       </c>
       <c r="S8">
-        <v>144.36000000000001</v>
+        <v>175.32</v>
       </c>
       <c r="T8">
-        <v>168.73</v>
+        <v>214.64</v>
       </c>
       <c r="U8">
-        <v>187</v>
+        <v>252.06</v>
       </c>
       <c r="V8">
-        <v>201.67</v>
+        <v>275.2</v>
       </c>
       <c r="W8">
-        <v>214.83</v>
+        <v>298.33999999999997</v>
       </c>
       <c r="X8">
-        <v>227.1</v>
+        <v>321.47000000000003</v>
       </c>
       <c r="Y8">
-        <v>238.63</v>
+        <v>344.61</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -12226,34 +12225,34 @@
         <v>-0.01</v>
       </c>
       <c r="P9">
-        <v>36.47</v>
+        <v>43.52</v>
       </c>
       <c r="Q9">
-        <v>72.650000000000006</v>
+        <v>86.46</v>
       </c>
       <c r="R9">
-        <v>106.84</v>
+        <v>128.63</v>
       </c>
       <c r="S9">
-        <v>137.88</v>
+        <v>165.8</v>
       </c>
       <c r="T9">
-        <v>162.91999999999999</v>
+        <v>202.74</v>
       </c>
       <c r="U9">
-        <v>181.75</v>
+        <v>238.38</v>
       </c>
       <c r="V9">
-        <v>196.48</v>
+        <v>261.61</v>
       </c>
       <c r="W9">
-        <v>209.48</v>
+        <v>282.81</v>
       </c>
       <c r="X9">
-        <v>221.58</v>
+        <v>304.01</v>
       </c>
       <c r="Y9">
-        <v>233.01</v>
+        <v>325.20999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -12300,34 +12299,34 @@
         <v>-0.01</v>
       </c>
       <c r="P10">
-        <v>34.090000000000003</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="Q10">
-        <v>67.97</v>
+        <v>80.84</v>
       </c>
       <c r="R10">
-        <v>100.09</v>
+        <v>120.38</v>
       </c>
       <c r="S10">
-        <v>129.84</v>
+        <v>155.04</v>
       </c>
       <c r="T10">
-        <v>155.26</v>
+        <v>189.43</v>
       </c>
       <c r="U10">
-        <v>174.95</v>
+        <v>223.34</v>
       </c>
       <c r="V10">
-        <v>189.94</v>
+        <v>244.16</v>
       </c>
       <c r="W10">
-        <v>202.85</v>
+        <v>264.97000000000003</v>
       </c>
       <c r="X10">
-        <v>214.69</v>
+        <v>285.08999999999997</v>
       </c>
       <c r="Y10">
-        <v>225.89</v>
+        <v>304.19</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -12374,34 +12373,34 @@
         <v>-0.01</v>
       </c>
       <c r="P11">
-        <v>31.45</v>
+        <v>37.56</v>
       </c>
       <c r="Q11">
-        <v>62.77</v>
+        <v>74.62</v>
       </c>
       <c r="R11">
-        <v>92.56</v>
+        <v>111.11</v>
       </c>
       <c r="S11">
-        <v>120.46</v>
+        <v>142.97</v>
       </c>
       <c r="T11">
-        <v>145.41999999999999</v>
+        <v>174.62</v>
       </c>
       <c r="U11">
-        <v>165.89</v>
+        <v>206.17</v>
       </c>
       <c r="V11">
-        <v>181.52</v>
+        <v>225.5</v>
       </c>
       <c r="W11">
-        <v>194.54</v>
+        <v>243.65</v>
       </c>
       <c r="X11">
-        <v>206.22</v>
+        <v>261.8</v>
       </c>
       <c r="Y11">
-        <v>217.1</v>
+        <v>279.95</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -12448,34 +12447,34 @@
         <v>-0.01</v>
       </c>
       <c r="P12">
-        <v>28.57</v>
+        <v>34.15</v>
       </c>
       <c r="Q12">
-        <v>57.08</v>
+        <v>67.84</v>
       </c>
       <c r="R12">
-        <v>84.29</v>
+        <v>100.94</v>
       </c>
       <c r="S12">
-        <v>109.94</v>
+        <v>129.94</v>
       </c>
       <c r="T12">
-        <v>133.63999999999999</v>
+        <v>158.33000000000001</v>
       </c>
       <c r="U12">
-        <v>154.05000000000001</v>
+        <v>186.72</v>
       </c>
       <c r="V12">
-        <v>170.3</v>
+        <v>205.6</v>
       </c>
       <c r="W12">
-        <v>183.74</v>
+        <v>221.14</v>
       </c>
       <c r="X12">
-        <v>195.52</v>
+        <v>236.58</v>
       </c>
       <c r="Y12">
-        <v>206.28</v>
+        <v>251.92</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -12522,34 +12521,34 @@
         <v>-0.01</v>
       </c>
       <c r="P13">
-        <v>25.47</v>
+        <v>30.47</v>
       </c>
       <c r="Q13">
-        <v>50.95</v>
+        <v>60.56</v>
       </c>
       <c r="R13">
-        <v>75.34</v>
+        <v>90.02</v>
       </c>
       <c r="S13">
-        <v>98.42</v>
+        <v>116.05</v>
       </c>
       <c r="T13">
-        <v>120.19</v>
+        <v>140.97</v>
       </c>
       <c r="U13">
-        <v>139.88</v>
+        <v>165.88</v>
       </c>
       <c r="V13">
-        <v>156.22999999999999</v>
+        <v>184.48</v>
       </c>
       <c r="W13">
-        <v>169.45</v>
+        <v>197</v>
       </c>
       <c r="X13">
-        <v>181.15</v>
+        <v>209.53</v>
       </c>
       <c r="Y13">
-        <v>191.94</v>
+        <v>222.06</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -12596,34 +12595,34 @@
         <v>-0.01</v>
       </c>
       <c r="P14">
-        <v>22.19</v>
+        <v>26.56</v>
       </c>
       <c r="Q14">
-        <v>44.42</v>
+        <v>52.83</v>
       </c>
       <c r="R14">
-        <v>65.78</v>
+        <v>78.430000000000007</v>
       </c>
       <c r="S14">
-        <v>86.04</v>
+        <v>101.4</v>
       </c>
       <c r="T14">
-        <v>105.36</v>
+        <v>122.65</v>
       </c>
       <c r="U14">
-        <v>123.45</v>
+        <v>143.9</v>
       </c>
       <c r="V14">
-        <v>139.56</v>
+        <v>162.69999999999999</v>
       </c>
       <c r="W14">
-        <v>152.61000000000001</v>
+        <v>172.11</v>
       </c>
       <c r="X14">
-        <v>163.58000000000001</v>
+        <v>181.53</v>
       </c>
       <c r="Y14">
-        <v>173.47</v>
+        <v>190.94</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -12670,34 +12669,34 @@
         <v>-0.01</v>
       </c>
       <c r="P15">
-        <v>18.739999999999998</v>
+        <v>22.45</v>
       </c>
       <c r="Q15">
-        <v>37.54</v>
+        <v>44.71</v>
       </c>
       <c r="R15">
-        <v>55.67</v>
+        <v>66.25</v>
       </c>
       <c r="S15">
-        <v>72.91</v>
+        <v>86.11</v>
       </c>
       <c r="T15">
-        <v>89.42</v>
+        <v>103.53</v>
       </c>
       <c r="U15">
-        <v>105.19</v>
+        <v>120.96</v>
       </c>
       <c r="V15">
-        <v>119.94</v>
+        <v>138.38999999999999</v>
       </c>
       <c r="W15">
-        <v>133.03</v>
+        <v>146.65</v>
       </c>
       <c r="X15">
-        <v>143.80000000000001</v>
+        <v>152.88</v>
       </c>
       <c r="Y15">
-        <v>153</v>
+        <v>159.11000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -12744,34 +12743,34 @@
         <v>-0.01</v>
       </c>
       <c r="P16">
-        <v>15.16</v>
+        <v>18.16</v>
       </c>
       <c r="Q16">
-        <v>30.37</v>
+        <v>36.270000000000003</v>
       </c>
       <c r="R16">
-        <v>45.11</v>
+        <v>53.58</v>
       </c>
       <c r="S16">
-        <v>59.15</v>
+        <v>70.28</v>
       </c>
       <c r="T16">
-        <v>72.599999999999994</v>
+        <v>83.75</v>
       </c>
       <c r="U16">
-        <v>85.66</v>
+        <v>97.22</v>
       </c>
       <c r="V16">
-        <v>98.24</v>
+        <v>110.69</v>
       </c>
       <c r="W16">
-        <v>110.04</v>
+        <v>120.8</v>
       </c>
       <c r="X16">
-        <v>120.54</v>
+        <v>123.9</v>
       </c>
       <c r="Y16">
-        <v>129.41</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -12818,34 +12817,34 @@
         <v>-0.01</v>
       </c>
       <c r="P17">
-        <v>11.46</v>
+        <v>13.74</v>
       </c>
       <c r="Q17">
-        <v>22.97</v>
+        <v>27.49</v>
       </c>
       <c r="R17">
-        <v>34.17</v>
+        <v>40.520000000000003</v>
       </c>
       <c r="S17">
-        <v>44.87</v>
+        <v>53.47</v>
       </c>
       <c r="T17">
-        <v>55.2</v>
+        <v>63.45</v>
       </c>
       <c r="U17">
-        <v>65.25</v>
+        <v>72.95</v>
       </c>
       <c r="V17">
-        <v>75.010000000000005</v>
+        <v>82.66</v>
       </c>
       <c r="W17">
-        <v>84.43</v>
+        <v>92.36</v>
       </c>
       <c r="X17">
-        <v>93.35</v>
+        <v>95.48</v>
       </c>
       <c r="Y17">
-        <v>101.42</v>
+        <v>95.52</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -12892,34 +12891,34 @@
         <v>-0.01</v>
       </c>
       <c r="P18">
-        <v>7.68</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="Q18">
-        <v>15.39</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="R18">
-        <v>22.95</v>
+        <v>27.15</v>
       </c>
       <c r="S18">
-        <v>30.19</v>
+        <v>35.659999999999997</v>
       </c>
       <c r="T18">
-        <v>37.31</v>
+        <v>43.06</v>
       </c>
       <c r="U18">
-        <v>44.15</v>
+        <v>48.73</v>
       </c>
       <c r="V18">
-        <v>50.78</v>
+        <v>54.39</v>
       </c>
       <c r="W18">
-        <v>57.21</v>
+        <v>60.06</v>
       </c>
       <c r="X18">
-        <v>63.44</v>
+        <v>66.41</v>
       </c>
       <c r="Y18">
-        <v>69.41</v>
+        <v>66.34</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -12966,34 +12965,34 @@
         <v>-0.01</v>
       </c>
       <c r="P19">
-        <v>3.85</v>
+        <v>4.62</v>
       </c>
       <c r="Q19">
-        <v>7.71</v>
+        <v>9.25</v>
       </c>
       <c r="R19">
-        <v>11.51</v>
+        <v>13.6</v>
       </c>
       <c r="S19">
-        <v>15.2</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="T19">
-        <v>18.88</v>
+        <v>22.29</v>
       </c>
       <c r="U19">
-        <v>22.41</v>
+        <v>24.24</v>
       </c>
       <c r="V19">
-        <v>25.76</v>
+        <v>25.91</v>
       </c>
       <c r="W19">
-        <v>28.98</v>
+        <v>29.62</v>
       </c>
       <c r="X19">
-        <v>32.090000000000003</v>
+        <v>33.32</v>
       </c>
       <c r="Y19">
-        <v>35.119999999999997</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -13043,7 +13042,7 @@
         <v>-0.01</v>
       </c>
       <c r="Q20">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R20">
         <v>-0.02</v>
@@ -13055,19 +13054,19 @@
         <v>-0.02</v>
       </c>
       <c r="U20">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="V20">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="W20">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="X20">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="Y20">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">

--- a/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
+++ b/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
@@ -1385,11 +1385,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-195327808"/>
-        <c:axId val="-195340864"/>
+        <c:axId val="1365717248"/>
+        <c:axId val="1365721056"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-195327808"/>
+        <c:axId val="1365717248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1432,7 +1432,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195340864"/>
+        <c:crossAx val="1365721056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1440,7 +1440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-195340864"/>
+        <c:axId val="1365721056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1491,7 +1491,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195327808"/>
+        <c:crossAx val="1365717248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2273,11 +2273,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-195332160"/>
-        <c:axId val="-195343040"/>
+        <c:axId val="1365719424"/>
+        <c:axId val="1365719968"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-195332160"/>
+        <c:axId val="1365719424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2320,7 +2320,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195343040"/>
+        <c:crossAx val="1365719968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2328,7 +2328,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-195343040"/>
+        <c:axId val="1365719968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2379,7 +2379,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195332160"/>
+        <c:crossAx val="1365719424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2982,34 +2982,34 @@
                   <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.13</c:v>
+                  <c:v>44.53</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>105.68</c:v>
+                  <c:v>88.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>156.88</c:v>
+                  <c:v>127.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>202.83</c:v>
+                  <c:v>156.63999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>245.33</c:v>
+                  <c:v>178.99</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>287.83999999999997</c:v>
+                  <c:v>197</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>325.43</c:v>
+                  <c:v>211.64</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>344.25</c:v>
+                  <c:v>224.47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>363.08</c:v>
+                  <c:v>236</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>381.9</c:v>
+                  <c:v>246.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3094,34 +3094,34 @@
                   <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.62</c:v>
+                  <c:v>-4.28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.25</c:v>
+                  <c:v>-8.6300000000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.6</c:v>
+                  <c:v>-12.92</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17.829999999999998</c:v>
+                  <c:v>-16.489999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.29</c:v>
+                  <c:v>-18.63</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24.24</c:v>
+                  <c:v>-18.71</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.91</c:v>
+                  <c:v>-18.309999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29.62</c:v>
+                  <c:v>-17.940000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>33.32</c:v>
+                  <c:v>-17.88</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37.03</c:v>
+                  <c:v>-18.16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3137,11 +3137,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-195342496"/>
-        <c:axId val="-195340320"/>
+        <c:axId val="1365723776"/>
+        <c:axId val="1365722144"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-195342496"/>
+        <c:axId val="1365723776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3184,7 +3184,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195340320"/>
+        <c:crossAx val="1365722144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3192,7 +3192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-195340320"/>
+        <c:axId val="1365722144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3243,7 +3243,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195342496"/>
+        <c:crossAx val="1365723776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,61 +3763,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>381.9</c:v>
+                  <c:v>246.71</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>381.19</c:v>
+                  <c:v>245.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>379.04</c:v>
+                  <c:v>243.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375.49</c:v>
+                  <c:v>240.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>370.55</c:v>
+                  <c:v>236.77</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>362.26</c:v>
+                  <c:v>231.46</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>344.61</c:v>
+                  <c:v>224.31</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>325.20999999999998</c:v>
+                  <c:v>214.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>304.19</c:v>
+                  <c:v>201.61</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>279.95</c:v>
+                  <c:v>183.39</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>251.92</c:v>
+                  <c:v>160.44999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>222.06</c:v>
+                  <c:v>134.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>190.94</c:v>
+                  <c:v>105.93</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>159.11000000000001</c:v>
+                  <c:v>76.459999999999994</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>127.1</c:v>
+                  <c:v>50.37</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>95.52</c:v>
+                  <c:v>27.47</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>66.34</c:v>
+                  <c:v>4.9400000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>37.03</c:v>
+                  <c:v>-18.16</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.02</c:v>
+                  <c:v>-44.19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4243,61 +4243,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>53.13</c:v>
+                  <c:v>44.53</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.92</c:v>
+                  <c:v>43.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>52.32</c:v>
+                  <c:v>42.37</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.32</c:v>
+                  <c:v>40.81</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>49.92</c:v>
+                  <c:v>38.93</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>48.15</c:v>
+                  <c:v>36.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.01</c:v>
+                  <c:v>34.29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.52</c:v>
+                  <c:v>31.58</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40.700000000000003</c:v>
+                  <c:v>28.63</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>37.56</c:v>
+                  <c:v>25.48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>34.15</c:v>
+                  <c:v>22.14</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30.47</c:v>
+                  <c:v>18.64</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>26.56</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>22.45</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>18.16</c:v>
+                  <c:v>7.42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13.74</c:v>
+                  <c:v>3.54</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.2200000000000006</c:v>
+                  <c:v>-0.37</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.62</c:v>
+                  <c:v>-4.28</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.01</c:v>
+                  <c:v>-8.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4313,11 +4313,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-195335968"/>
-        <c:axId val="-195332704"/>
+        <c:axId val="1365724320"/>
+        <c:axId val="1365723232"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-195335968"/>
+        <c:axId val="1365724320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4360,7 +4360,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195332704"/>
+        <c:crossAx val="1365723232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4368,7 +4368,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-195332704"/>
+        <c:axId val="1365723232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4419,7 +4419,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195335968"/>
+        <c:crossAx val="1365724320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4924,11 +4924,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-195341952"/>
-        <c:axId val="-195339232"/>
+        <c:axId val="1365724864"/>
+        <c:axId val="1365725952"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-195341952"/>
+        <c:axId val="1365724864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4970,7 +4970,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195339232"/>
+        <c:crossAx val="1365725952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4978,7 +4978,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-195339232"/>
+        <c:axId val="1365725952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5029,7 +5029,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195341952"/>
+        <c:crossAx val="1365724864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5387,11 +5387,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-195329984"/>
-        <c:axId val="-195335424"/>
+        <c:axId val="1141607216"/>
+        <c:axId val="1141600688"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-195329984"/>
+        <c:axId val="1141607216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5433,7 +5433,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195335424"/>
+        <c:crossAx val="1141600688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5441,7 +5441,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-195335424"/>
+        <c:axId val="1141600688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5492,7 +5492,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-195329984"/>
+        <c:crossAx val="1141607216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11707,34 +11707,34 @@
         <v>-0.01</v>
       </c>
       <c r="P2">
-        <v>53.13</v>
+        <v>44.53</v>
       </c>
       <c r="Q2">
-        <v>105.68</v>
+        <v>88.52</v>
       </c>
       <c r="R2">
-        <v>156.88</v>
+        <v>127.42</v>
       </c>
       <c r="S2">
-        <v>202.83</v>
+        <v>156.63999999999999</v>
       </c>
       <c r="T2">
-        <v>245.33</v>
+        <v>178.99</v>
       </c>
       <c r="U2">
-        <v>287.83999999999997</v>
+        <v>197</v>
       </c>
       <c r="V2">
-        <v>325.43</v>
+        <v>211.64</v>
       </c>
       <c r="W2">
-        <v>344.25</v>
+        <v>224.47</v>
       </c>
       <c r="X2">
-        <v>363.08</v>
+        <v>236</v>
       </c>
       <c r="Y2">
-        <v>381.9</v>
+        <v>246.71</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -11781,34 +11781,34 @@
         <v>-0.01</v>
       </c>
       <c r="P3">
-        <v>52.92</v>
+        <v>43.62</v>
       </c>
       <c r="Q3">
-        <v>105.29</v>
+        <v>86.7</v>
       </c>
       <c r="R3">
-        <v>156.30000000000001</v>
+        <v>124.97</v>
       </c>
       <c r="S3">
-        <v>202.18</v>
+        <v>154.63</v>
       </c>
       <c r="T3">
-        <v>244.53</v>
+        <v>177.33</v>
       </c>
       <c r="U3">
-        <v>286.87</v>
+        <v>195.56</v>
       </c>
       <c r="V3">
-        <v>322.89999999999998</v>
+        <v>210.33</v>
       </c>
       <c r="W3">
-        <v>343.68</v>
+        <v>223.27</v>
       </c>
       <c r="X3">
-        <v>362.43</v>
+        <v>234.88</v>
       </c>
       <c r="Y3">
-        <v>381.19</v>
+        <v>245.62</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -11855,34 +11855,34 @@
         <v>-0.01</v>
       </c>
       <c r="P4">
-        <v>52.32</v>
+        <v>42.37</v>
       </c>
       <c r="Q4">
-        <v>104.13</v>
+        <v>84.22</v>
       </c>
       <c r="R4">
-        <v>154.55000000000001</v>
+        <v>121.56</v>
       </c>
       <c r="S4">
-        <v>200.25</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="T4">
-        <v>242.11</v>
+        <v>174.63</v>
       </c>
       <c r="U4">
-        <v>283.95999999999998</v>
+        <v>193.19</v>
       </c>
       <c r="V4">
-        <v>316.31</v>
+        <v>208.12</v>
       </c>
       <c r="W4">
-        <v>341.96</v>
+        <v>221.19</v>
       </c>
       <c r="X4">
-        <v>360.5</v>
+        <v>232.89</v>
       </c>
       <c r="Y4">
-        <v>379.04</v>
+        <v>243.65</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -11929,34 +11929,34 @@
         <v>-0.01</v>
       </c>
       <c r="P5">
-        <v>51.32</v>
+        <v>40.81</v>
       </c>
       <c r="Q5">
-        <v>102.13</v>
+        <v>81.12</v>
       </c>
       <c r="R5">
-        <v>151.65</v>
+        <v>117.21</v>
       </c>
       <c r="S5">
-        <v>196.47</v>
+        <v>146.97</v>
       </c>
       <c r="T5">
-        <v>238.09</v>
+        <v>170.74</v>
       </c>
       <c r="U5">
-        <v>279.14999999999998</v>
+        <v>189.72</v>
       </c>
       <c r="V5">
-        <v>308.18</v>
+        <v>204.9</v>
       </c>
       <c r="W5">
-        <v>336.04</v>
+        <v>218.11</v>
       </c>
       <c r="X5">
-        <v>357.3</v>
+        <v>229.95</v>
       </c>
       <c r="Y5">
-        <v>375.49</v>
+        <v>240.75</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -12003,34 +12003,34 @@
         <v>-0.01</v>
       </c>
       <c r="P6">
-        <v>49.92</v>
+        <v>38.93</v>
       </c>
       <c r="Q6">
-        <v>99.3</v>
+        <v>77.41</v>
       </c>
       <c r="R6">
-        <v>147.55000000000001</v>
+        <v>111.94</v>
       </c>
       <c r="S6">
-        <v>190.72</v>
+        <v>141.02000000000001</v>
       </c>
       <c r="T6">
-        <v>232.51</v>
+        <v>165.37</v>
       </c>
       <c r="U6">
-        <v>272.08999999999997</v>
+        <v>184.91</v>
       </c>
       <c r="V6">
-        <v>298.57</v>
+        <v>200.46</v>
       </c>
       <c r="W6">
-        <v>325.05</v>
+        <v>213.83</v>
       </c>
       <c r="X6">
-        <v>351.53</v>
+        <v>225.86</v>
       </c>
       <c r="Y6">
-        <v>370.55</v>
+        <v>236.77</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -12077,34 +12077,34 @@
         <v>-0.01</v>
       </c>
       <c r="P7">
-        <v>48.15</v>
+        <v>36.75</v>
       </c>
       <c r="Q7">
-        <v>95.73</v>
+        <v>73.13</v>
       </c>
       <c r="R7">
-        <v>142.25</v>
+        <v>105.83</v>
       </c>
       <c r="S7">
-        <v>183.65</v>
+        <v>133.72999999999999</v>
       </c>
       <c r="T7">
-        <v>225.05</v>
+        <v>158.1</v>
       </c>
       <c r="U7">
-        <v>262.64</v>
+        <v>178.4</v>
       </c>
       <c r="V7">
-        <v>287.55</v>
+        <v>194.54</v>
       </c>
       <c r="W7">
-        <v>312.45</v>
+        <v>208.12</v>
       </c>
       <c r="X7">
-        <v>337.35</v>
+        <v>220.32</v>
       </c>
       <c r="Y7">
-        <v>362.26</v>
+        <v>231.46</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -12151,34 +12151,34 @@
         <v>-0.01</v>
       </c>
       <c r="P8">
-        <v>46.01</v>
+        <v>34.29</v>
       </c>
       <c r="Q8">
-        <v>91.43</v>
+        <v>68.290000000000006</v>
       </c>
       <c r="R8">
-        <v>136</v>
+        <v>98.99</v>
       </c>
       <c r="S8">
-        <v>175.32</v>
+        <v>125.2</v>
       </c>
       <c r="T8">
-        <v>214.64</v>
+        <v>148.77000000000001</v>
       </c>
       <c r="U8">
-        <v>252.06</v>
+        <v>169.57</v>
       </c>
       <c r="V8">
-        <v>275.2</v>
+        <v>186.64</v>
       </c>
       <c r="W8">
-        <v>298.33999999999997</v>
+        <v>200.61</v>
       </c>
       <c r="X8">
-        <v>321.47000000000003</v>
+        <v>212.97</v>
       </c>
       <c r="Y8">
-        <v>344.61</v>
+        <v>224.31</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -12225,34 +12225,34 @@
         <v>-0.01</v>
       </c>
       <c r="P9">
-        <v>43.52</v>
+        <v>31.58</v>
       </c>
       <c r="Q9">
-        <v>86.46</v>
+        <v>62.93</v>
       </c>
       <c r="R9">
-        <v>128.63</v>
+        <v>91.44</v>
       </c>
       <c r="S9">
-        <v>165.8</v>
+        <v>115.61</v>
       </c>
       <c r="T9">
-        <v>202.74</v>
+        <v>137.68</v>
       </c>
       <c r="U9">
-        <v>238.38</v>
+        <v>157.94</v>
       </c>
       <c r="V9">
-        <v>261.61</v>
+        <v>175.76</v>
       </c>
       <c r="W9">
-        <v>282.81</v>
+        <v>190.49</v>
       </c>
       <c r="X9">
-        <v>304.01</v>
+        <v>203.23</v>
       </c>
       <c r="Y9">
-        <v>325.20999999999998</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -12299,34 +12299,34 @@
         <v>-0.01</v>
       </c>
       <c r="P10">
-        <v>40.700000000000003</v>
+        <v>28.63</v>
       </c>
       <c r="Q10">
-        <v>80.84</v>
+        <v>57.09</v>
       </c>
       <c r="R10">
-        <v>120.38</v>
+        <v>83.23</v>
       </c>
       <c r="S10">
-        <v>155.04</v>
+        <v>105.17</v>
       </c>
       <c r="T10">
-        <v>189.43</v>
+        <v>125.17</v>
       </c>
       <c r="U10">
-        <v>223.34</v>
+        <v>143.94999999999999</v>
       </c>
       <c r="V10">
-        <v>244.16</v>
+        <v>161.36000000000001</v>
       </c>
       <c r="W10">
-        <v>264.97000000000003</v>
+        <v>176.55</v>
       </c>
       <c r="X10">
-        <v>285.08999999999997</v>
+        <v>189.69</v>
       </c>
       <c r="Y10">
-        <v>304.19</v>
+        <v>201.61</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -12373,34 +12373,34 @@
         <v>-0.01</v>
       </c>
       <c r="P11">
-        <v>37.56</v>
+        <v>25.48</v>
       </c>
       <c r="Q11">
-        <v>74.62</v>
+        <v>50.8</v>
       </c>
       <c r="R11">
-        <v>111.11</v>
+        <v>74.36</v>
       </c>
       <c r="S11">
-        <v>142.97</v>
+        <v>93.96</v>
       </c>
       <c r="T11">
-        <v>174.62</v>
+        <v>111.61</v>
       </c>
       <c r="U11">
-        <v>206.17</v>
+        <v>128.24</v>
       </c>
       <c r="V11">
-        <v>225.5</v>
+        <v>144.04</v>
       </c>
       <c r="W11">
-        <v>243.65</v>
+        <v>158.72999999999999</v>
       </c>
       <c r="X11">
-        <v>261.8</v>
+        <v>171.67</v>
       </c>
       <c r="Y11">
-        <v>279.95</v>
+        <v>183.39</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -12447,34 +12447,34 @@
         <v>-0.01</v>
       </c>
       <c r="P12">
-        <v>34.15</v>
+        <v>22.14</v>
       </c>
       <c r="Q12">
-        <v>67.84</v>
+        <v>44.12</v>
       </c>
       <c r="R12">
-        <v>100.94</v>
+        <v>64.86</v>
       </c>
       <c r="S12">
-        <v>129.94</v>
+        <v>82.06</v>
       </c>
       <c r="T12">
-        <v>158.33000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="U12">
-        <v>186.72</v>
+        <v>111.34</v>
       </c>
       <c r="V12">
-        <v>205.6</v>
+        <v>124.88</v>
       </c>
       <c r="W12">
-        <v>221.14</v>
+        <v>137.81</v>
       </c>
       <c r="X12">
-        <v>236.58</v>
+        <v>149.80000000000001</v>
       </c>
       <c r="Y12">
-        <v>251.92</v>
+        <v>160.44999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -12521,34 +12521,34 @@
         <v>-0.01</v>
       </c>
       <c r="P13">
-        <v>30.47</v>
+        <v>18.64</v>
       </c>
       <c r="Q13">
-        <v>60.56</v>
+        <v>37.090000000000003</v>
       </c>
       <c r="R13">
-        <v>90.02</v>
+        <v>54.74</v>
       </c>
       <c r="S13">
-        <v>116.05</v>
+        <v>69.5</v>
       </c>
       <c r="T13">
-        <v>140.97</v>
+        <v>81.97</v>
       </c>
       <c r="U13">
-        <v>165.88</v>
+        <v>93.48</v>
       </c>
       <c r="V13">
-        <v>184.48</v>
+        <v>104.43</v>
       </c>
       <c r="W13">
-        <v>197</v>
+        <v>114.98</v>
       </c>
       <c r="X13">
-        <v>209.53</v>
+        <v>125.09</v>
       </c>
       <c r="Y13">
-        <v>222.06</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -12595,34 +12595,34 @@
         <v>-0.01</v>
       </c>
       <c r="P14">
-        <v>26.56</v>
+        <v>15</v>
       </c>
       <c r="Q14">
-        <v>52.83</v>
+        <v>29.77</v>
       </c>
       <c r="R14">
-        <v>78.430000000000007</v>
+        <v>44.09</v>
       </c>
       <c r="S14">
-        <v>101.4</v>
+        <v>56.31</v>
       </c>
       <c r="T14">
-        <v>122.65</v>
+        <v>66.09</v>
       </c>
       <c r="U14">
-        <v>143.9</v>
+        <v>74.83</v>
       </c>
       <c r="V14">
-        <v>162.69999999999999</v>
+        <v>83.01</v>
       </c>
       <c r="W14">
-        <v>172.11</v>
+        <v>90.87</v>
       </c>
       <c r="X14">
-        <v>181.53</v>
+        <v>98.52</v>
       </c>
       <c r="Y14">
-        <v>190.94</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -12669,34 +12669,34 @@
         <v>-0.01</v>
       </c>
       <c r="P15">
-        <v>22.45</v>
+        <v>11.25</v>
       </c>
       <c r="Q15">
-        <v>44.71</v>
+        <v>22.25</v>
       </c>
       <c r="R15">
-        <v>66.25</v>
+        <v>32.979999999999997</v>
       </c>
       <c r="S15">
-        <v>86.11</v>
+        <v>42.44</v>
       </c>
       <c r="T15">
-        <v>103.53</v>
+        <v>49.58</v>
       </c>
       <c r="U15">
-        <v>120.96</v>
+        <v>55.59</v>
       </c>
       <c r="V15">
-        <v>138.38999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="W15">
-        <v>146.65</v>
+        <v>66.34</v>
       </c>
       <c r="X15">
-        <v>152.88</v>
+        <v>71.44</v>
       </c>
       <c r="Y15">
-        <v>159.11000000000001</v>
+        <v>76.459999999999994</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -12743,34 +12743,34 @@
         <v>-0.01</v>
       </c>
       <c r="P16">
-        <v>18.16</v>
+        <v>7.42</v>
       </c>
       <c r="Q16">
-        <v>36.270000000000003</v>
+        <v>14.59</v>
       </c>
       <c r="R16">
-        <v>53.58</v>
+        <v>21.54</v>
       </c>
       <c r="S16">
-        <v>70.28</v>
+        <v>27.88</v>
       </c>
       <c r="T16">
-        <v>83.75</v>
+        <v>32.72</v>
       </c>
       <c r="U16">
-        <v>97.22</v>
+        <v>36.32</v>
       </c>
       <c r="V16">
-        <v>110.69</v>
+        <v>39.479999999999997</v>
       </c>
       <c r="W16">
-        <v>120.8</v>
+        <v>42.63</v>
       </c>
       <c r="X16">
-        <v>123.9</v>
+        <v>46.25</v>
       </c>
       <c r="Y16">
-        <v>127.1</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -12817,34 +12817,34 @@
         <v>-0.01</v>
       </c>
       <c r="P17">
-        <v>13.74</v>
+        <v>3.54</v>
       </c>
       <c r="Q17">
-        <v>27.49</v>
+        <v>6.86</v>
       </c>
       <c r="R17">
-        <v>40.520000000000003</v>
+        <v>9.99</v>
       </c>
       <c r="S17">
-        <v>53.47</v>
+        <v>12.98</v>
       </c>
       <c r="T17">
-        <v>63.45</v>
+        <v>15.58</v>
       </c>
       <c r="U17">
-        <v>72.95</v>
+        <v>17.28</v>
       </c>
       <c r="V17">
-        <v>82.66</v>
+        <v>19.22</v>
       </c>
       <c r="W17">
-        <v>92.36</v>
+        <v>21.85</v>
       </c>
       <c r="X17">
-        <v>95.48</v>
+        <v>24.64</v>
       </c>
       <c r="Y17">
-        <v>95.52</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -12891,34 +12891,34 @@
         <v>-0.01</v>
       </c>
       <c r="P18">
-        <v>9.2200000000000006</v>
+        <v>-0.37</v>
       </c>
       <c r="Q18">
-        <v>18.440000000000001</v>
+        <v>-0.9</v>
       </c>
       <c r="R18">
-        <v>27.15</v>
+        <v>-1.55</v>
       </c>
       <c r="S18">
-        <v>35.659999999999997</v>
+        <v>-1.87</v>
       </c>
       <c r="T18">
-        <v>43.06</v>
+        <v>-1.8</v>
       </c>
       <c r="U18">
-        <v>48.73</v>
+        <v>-0.79</v>
       </c>
       <c r="V18">
-        <v>54.39</v>
+        <v>0.78</v>
       </c>
       <c r="W18">
-        <v>60.06</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="X18">
-        <v>66.41</v>
+        <v>3.63</v>
       </c>
       <c r="Y18">
-        <v>66.34</v>
+        <v>4.9400000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -12965,34 +12965,34 @@
         <v>-0.01</v>
       </c>
       <c r="P19">
-        <v>4.62</v>
+        <v>-4.28</v>
       </c>
       <c r="Q19">
-        <v>9.25</v>
+        <v>-8.6300000000000008</v>
       </c>
       <c r="R19">
-        <v>13.6</v>
+        <v>-12.92</v>
       </c>
       <c r="S19">
-        <v>17.829999999999998</v>
+        <v>-16.489999999999998</v>
       </c>
       <c r="T19">
-        <v>22.29</v>
+        <v>-18.63</v>
       </c>
       <c r="U19">
-        <v>24.24</v>
+        <v>-18.71</v>
       </c>
       <c r="V19">
-        <v>25.91</v>
+        <v>-18.309999999999999</v>
       </c>
       <c r="W19">
-        <v>29.62</v>
+        <v>-17.940000000000001</v>
       </c>
       <c r="X19">
-        <v>33.32</v>
+        <v>-17.88</v>
       </c>
       <c r="Y19">
-        <v>37.03</v>
+        <v>-18.16</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -13039,34 +13039,34 @@
         <v>-0.01</v>
       </c>
       <c r="P20">
-        <v>-0.01</v>
+        <v>-8.15</v>
       </c>
       <c r="Q20">
-        <v>-0.01</v>
+        <v>-16.29</v>
       </c>
       <c r="R20">
-        <v>-0.02</v>
+        <v>-24.05</v>
       </c>
       <c r="S20">
-        <v>-0.02</v>
+        <v>-30.65</v>
       </c>
       <c r="T20">
-        <v>-0.02</v>
+        <v>-34.619999999999997</v>
       </c>
       <c r="U20">
-        <v>-0.02</v>
+        <v>-36.979999999999997</v>
       </c>
       <c r="V20">
-        <v>-0.02</v>
+        <v>-38.9</v>
       </c>
       <c r="W20">
-        <v>-0.02</v>
+        <v>-40.67</v>
       </c>
       <c r="X20">
-        <v>-0.02</v>
+        <v>-42.41</v>
       </c>
       <c r="Y20">
-        <v>-0.02</v>
+        <v>-44.19</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
